--- a/test-science-documents-library.xlsx
+++ b/test-science-documents-library.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jhaman\Documents\test-science-documents-library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25B711A7-84A0-4FDA-AF57-8B360CD12C50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F95CBB5-77DF-4D03-AF82-FE0F8DB59DDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30612" yWindow="348" windowWidth="30936" windowHeight="17040" tabRatio="212" activeTab="1" xr2:uid="{0ADD57B5-79F8-4915-B656-B2883E0E3CC2}"/>
+    <workbookView xWindow="-103" yWindow="343" windowWidth="33120" windowHeight="18274" tabRatio="212" xr2:uid="{0ADD57B5-79F8-4915-B656-B2883E0E3CC2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1249" uniqueCount="881">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1249" uniqueCount="879">
   <si>
     <t>Project</t>
   </si>
@@ -200,9 +200,6 @@
   </si>
   <si>
     <t>https://testscience.org/wp-content/uploads/formidable/20/Comparing-Computer-Experiments-for-the-Gaussian-Process-Model-Using-Integrated-Prediction-Varian.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Space filling designs are a common choice of experimental design strategy for computer experiments. This paper compares space filling design types based on their theoretical prediction variance properties with respect to the Gaussian Process model. </t>
   </si>
   <si>
     <t>Comparing Normal and Binary D-Optimal Designs by Statistical Power</t>
@@ -429,9 +426,6 @@
   </si>
   <si>
     <t>Was this published in ITEA J?</t>
-  </si>
-  <si>
-    <t>Defense, Operational Testing, Design of Experiments, Modeling &amp; Simulation</t>
   </si>
   <si>
     <t>Statistical Models for Combining Information Stryker Reliability Case Study</t>
@@ -815,21 +809,9 @@
     <t>Combining Information, Defense Acquisition, Exponential Distribution, Reliability, Weibull Distribution</t>
   </si>
   <si>
-    <t>Statistics, Operational Testing, Design of Experiments, Modeling and Simulation, Validation</t>
-  </si>
-  <si>
-    <t>Design of Experiments, Operational Testing, Statistics</t>
-  </si>
-  <si>
-    <t>Design of Experiment, Operational Testing, Statistics</t>
-  </si>
-  <si>
     <t>Data, Data Management, Metadata</t>
   </si>
   <si>
-    <t>Design of Experiments, Operational Testing, Statistical Analysis</t>
-  </si>
-  <si>
     <t xml:space="preserve">Situation Awareness (SA) plays a key role in decision making and human performance, higher operator SA is associated with increased operator performance and decreased operator errors. While maintaining or improving “situational awareness” is a common requirement for systems under test, there is no single standardized method or metric for quantifying SA in operational testing (OT). This leads to varied and sometimes suboptimal treatments of SA measurement across programs and test events. This paper introduces Endsley’s three-level model of SA in dynamic decision making, a frequently used model of individual SA, reviews trade-offs in some existing measures of SA, and discusses a selection of potential ways in which SA measurement during OT may be improved. </t>
   </si>
   <si>
@@ -902,9 +884,6 @@
     <t>This training provides details regarding the use of design of experiments, from choosing proper response variables, to identifying factors that could affect such responses, to determining the amount of data necessary to collect. The training also explains the benefits of using a Design of Experiments approach to testing and provides an overview of commonly used designs (e.g., factorial, optimal, and space-filling). The briefing illustrates the concepts discussed using several case studies.</t>
   </si>
   <si>
-    <t>Modeling and Simulation (M&amp;S) Validation, Torpedo, Design of Experiments, Undersea Warfare</t>
-  </si>
-  <si>
     <t>Design of Experiments, ITEA, Test and Evaluation</t>
   </si>
   <si>
@@ -1001,9 +980,6 @@
     <t>We illustrate the construction of Bayesian D-optimal designs for nonlinear models and compare the relative efficiency of standard designs with these designs for several models and prior distributions on the parameters. Through a relative efficiency analysis, we show that standard designs can perform well in situations where the nonlinear model is intrinsically linear. However, if the model is nonlinear and its expectation function cannot be linearized by simple transformations, the nonlinear optimal design is considerably more efficient than the standard design.</t>
   </si>
   <si>
-    <t>The areas of application for design of experiments principles have evolved, mimicking the growth of U.S. industries over the last century, from agriculture to manufacturing to chemical and process industries to the services and government sectors. In addition, statistically based quality pro- grams adopted by businesses morphed from total quality management to Six Sigma and, most recently, statistical engineering (see Hoerl and Snee 2010). The good news about these transformations is that each evolution con- tains more technical substance, embedding the methodologies as core compe- tencies, and is less of a ‘‘program.’’ Design of experiments is fundamental to statistical engineering and is receiving increased attention within large govern- ment agencies such as the National Aeronautics and Space Administration (NASA) and the Department of Defense. Because test policy is intended to shape test programs, numerous test agencies have experimented with policy wording since about 2001. The Director of Operational Test &amp; Evaluation has recently (2010) published guidelines to mold test programs into a sequence of well-designed and statistically defensible experiments. Specifically, the guide- lines require, for the first time, that test programs report statistical power as one proof of sound test design. This article presents the underlying tenents of design of experiments, as applied in the Department of Defense, focusing on factorial, fractional factorial, and response surface design and analyses. The concepts of statistical modeling and sequential experimentation are also emphasized. Military applications are presented for testing and evaluation of weapon system acquisition, including force-on-force tactics, weapons employment and maritime search, identification, and intercept.</t>
-  </si>
-  <si>
     <t>In many situations, collecting sufficient data to evaluate system performance against operationally realistic threats is not possible due to cost and resource restrictions, safety concerns, or lack of adequate or representative threats. Modeling and simulation tools that have been verified, validated, and accredited can be used to supplement live testing in order to facilitate a more complete evaluation of performance. Two key questions that frequently arise when planning an operational test are (1) which (and how many) points within the operational space should be chosen in the simulation space and the live space for optimal ability to verify and validate the M&amp;S, and (2) once that data is collected, what is the best way to compare the live trials to the simulated trials for the purpose of validating the M&amp;S? This conference presentation addresses various strategies for addressing these two questions. The best methodologies for designing and analyzing will vary depending on the goal of operational test, the type of model used in the simulation, and the amount of live and simulated data available.</t>
   </si>
   <si>
@@ -1013,9 +989,6 @@
     <t>While the human brain is powerful tool for quickly recognizing patterns in data, it will frequently make errors in interpreting random data. Luckily, these mistakes occur in systematic and predictable ways. Statistical models provide an analytical framework that helps us avoid these error-prone heuristics and draw accurate conclusions from random data. This non-technical presentation highlights some tricks of the trade learned by studying data and the way the human brain processes. First, we introduce statistics as the science of data, and discuss how the popular conception of randomness differs from its technical definition. Later sections highlight the human brain as a pattern recognition machine. Examples from published literature and media highlight systematic and predicable errors in human cognition as well as how poor data analysis and graphical displays can cause critical errors in analysis. Finally, we'll talk about using statistical models for analysis, including how violations of model assumptions should effect our analyses.</t>
   </si>
   <si>
-    <t>Reliability tests determine which factors drive system reliability. Often, the reliability or failure time data collected in these tests tend to follow distinctly non- normal distributions and include censored observations. The experimental design should accommodate the skewed nature of the response and allow for censored observations, which occur when systems under test do not fail within the allotted test time. To account for these design and analysis considerations, Monte Carlo simulations are frequently used to evaluate experimental design properties. Simulation provides accurate power calculations as a function of sample size, allowing researchers to determine adequate sample sizes at each level of the treatment. However, simulation may be inefficient for comparing multiple experiments of various sizes. In this document, we present a closed form approach for calculating power, based on the non- central chi-squared approximation to the distribution of the likelihood ratio statistic. The solution can be used to compare multiple designs and accommodate trade-space analyses between power, efTect size, model formulation, sample size, censoring rates, and design type. To demonstrate the efficiency of our approach, we provide a comparison to estimates that are generated using Monte Carlo simulation.</t>
-  </si>
-  <si>
     <t>Analyses are reproducible if the same methods applied to the same data produce identical results when run again by another researcher (or you in the future). Reproducible analyses are transparent and easy for reviewers to verify, as results and figures can be traced directly to the data and methods that produced them. There are also direct benefits to the researcher. Real-world analysis workflows inevitably require changes to incorporate new or additional data, or to address feedback from collaborators, reviewers, or sponsors.</t>
   </si>
   <si>
@@ -1139,9 +1112,6 @@
     <t>Matthew Avery</t>
   </si>
   <si>
-    <t>Alyson Wilson, Kassandra Froncyzk</t>
-  </si>
-  <si>
     <t>V. Bram Lillard</t>
   </si>
   <si>
@@ -1367,9 +1337,6 @@
     <t>https://www.youtube.com/watch?v=qVPtm43prdU</t>
   </si>
   <si>
-    <t>Problem  Reliability is an essential element in assessing the operational suitability of Department of Defense weapon systems. Reliability takes a prominent role in both the design and analysis of operational tests. In the current era of reduced budgets and increased reliability requirements, it is challenging to verify reliability requirements in a single test. Furthermore, all available data should be considered in order to ensure evaluations provide the most appropriate analysis of the system’s reliability. Approach  This paper describes the benefits of using parametric statistical models to combine infor- mation across multiple testing events. Both frequentist and Bayesian inference techniques are employed and they are compared and contrasted to illustrate di↵erent statistical methods for combining information. We apply these methods to data collected during the developmental and operational test phases for the Stryker family of vehicles. Results  We show that, when we combine the available information across two test phases for the Stryker family of vehicles, reliability estimates are more accurate and precise than those reported previously using traditional methods that use only operational test data in their reliability assessments.</t>
-  </si>
-  <si>
     <t>For many systems, testing is expensive and only a few live test events are conducted. When this occurs, testers frequently use a model to extend the test results. However, testers must validate the model to show that it is an accurate representation of the real world from the perspective of the intended uses of the model. This raises a problem  when only a small number of live test events are conducted, only limited data are available to validate the model, and some testers struggle with model validation. This article describes a statistically rigorous approach for validating a model with only a small number of live test results. We discuss a specific application for validating a model of a naval surface combatant defending itself against a cruise missile attack. The approach takes into account potential correlation in the data and other factors that may drive system performance.</t>
   </si>
   <si>
@@ -1634,18 +1601,6 @@
     <t>The ITEA Journal of Test and Evaluation</t>
   </si>
   <si>
-    <t>Thomas, Dean, and Rebecca Dickinson. “Validating the Probability of Raid Annihilation Testbed Using a Statistical Approach.” The The ITEA Journal of Test and Evaluation 36, no. 2 (June 2015).</t>
-  </si>
-  <si>
-    <t>Wojton, Heather, Kelly Avery, Laura Freeman, and Thomas Johnson. “Designing Experiments for Model Validation – The Foundations for Uncertainty Quantification.” The The ITEA Journal of Test and Evaluation 40, no. 1 (2019).</t>
-  </si>
-  <si>
-    <t>could link to the The ITEA Journal of Test and Evaluation paper.</t>
-  </si>
-  <si>
-    <t>Medlin, Rebecca, and Andrew Flack. “Managing T&amp;E Data to Encourage Reuse.” The The ITEA Journal of Test and Evaluation of Test and Evaluation, 2019.</t>
-  </si>
-  <si>
     <t>The The ITEA Journal of Test and Evaluation of Test and Evaluation</t>
   </si>
   <si>
@@ -1846,9 +1801,6 @@
     <t>This document outlines the charter for the Committee to Institutionalize Scientific Test Design and Rigor in Test and Evaluation. The charter defines the problem, identifies potential steps in a roadmap for accomplishing the goals of the committee and lists committeemembership. Once the committee is assembled, the members will revise this document as needed. The charter will be endorsed by DOT&amp;E and DDT&amp;E, once finalize.</t>
   </si>
   <si>
-    <t>The The ITEA Journal of Test and Evaluation</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">Avery, Kelly, Laura Freeman, and Rebecca Medlin. </t>
     </r>
@@ -4062,12 +4014,6 @@
     <t>Pilot Training Next- Modeling Skill Transfer in a Military Learning Environment</t>
   </si>
   <si>
-    <t>Operational Testing, Design of Experiments, Live Fire Test and Evaluation, Sequential Design, Sensitivity Testing</t>
-  </si>
-  <si>
-    <t>Department of Defense, Reliability, Reliability Growth, Reliability Analysis, Test and Evaluation Master Plan</t>
-  </si>
-  <si>
     <t>Cyber Assessments, Cyber Testing, Design of Experiments</t>
   </si>
   <si>
@@ -4075,9 +4021,6 @@
   </si>
   <si>
     <t>Reliability, Bayesian, Bayes</t>
-  </si>
-  <si>
-    <t>A presentation on the theory and practive of observational studies.  Specific average treatment effect methods include matching, difference-in-difference estimators, and instrumental variables.</t>
   </si>
   <si>
     <t>This document contains the technical content for the Scientific Test and Analysis Techniques (STAT) in Test and Evaluation (T&amp;E) continuous learning module. The module provides a basic understanding of STAT in T&amp;E. Topics covered include design of experiments, observational studies, survey design and analysis, and statistical analysis. It is designed as a four hour online course, suitable for inclusion in the DAU T&amp;E certification curriculum.</t>
@@ -4155,9 +4098,6 @@
     <t>Effective training of the broad set of users/operators of systems has downstream impacts on usability, workload, and ultimate system performance that are related to mission success. In order to measure training effectiveness, we designed a survey called the Operational Assessment of Training Scale (OATS) in partnership with the Army Test and Evaluation Center (ATEC). Two subscales were designed to assess the degrees to which training covered relevant content for real operations (Relevance subscale) and enabled self-rated ability to interact with systems effectively after training (Efficacy subscale). The full list of 15 items were given to over 700 users/operators across a range of military systems and test events (comprising both developmental and operational testing phases). Systems included vehicles, aircraft, C3 systems, and dismounted squad equipment, among other types. We evaluated reliability of the factor structure across these military samples using confirmatory factor analysis. We confirmed that OATS exhibited a two-factor structure for training relevance and training efficacy. Additionally, a shortened, six-item measure of the OATS with three items per subscale continues to fit observed data well, allowing for quicker assessments of training. We discuss various ways that the OATS can be applied to one-off, multi-day, multi-event, and other types of training events. Additional OATS details and information about other scales for test and evaluation are available at the Institute for Defense Analyses' website, https://testscience.org/validated-scales-repository/.</t>
   </si>
   <si>
-    <t>In the acquisition and testing world, data analysts repeatedly encounter certain categories of data, such as time or distance until an event (e.g., failure, alert, detection), binary outcomes (e.g., success/failure, hit/miss), and survey responses. Analysts need tools that enable them to produce quality and timely analyses of the data they acquire during testing. This poster presents four web-based apps that can analyze these types of data. The apps are designed to assist analysts and researchers with simple repeatable analysis tasks, such as building summary tables and plots for reports or briefings. Using software tools like these apps can inclease repti)ducibility of results, timeliness of analysis and reporting, attractiveness and standardization of aesthetics in figures, and accuracy of results. The first app models reliability ofa system or component by fitting parametric statistical distributions to time-to-failure data. The second app fits a logistic regression model to binary data with one or two independent continuous variables as The third calculates summary statistics and produces plots of groups of Likert-scale survey question responses. The fourth calculates the system usability scale (SUS) scores for SUS survey responses and enables the app user to plot scores versus an independent variable. These apps are available for public use on the Test Science Interactive Tools webpage https://testscience.org/interactive-tools/.</t>
-  </si>
-  <si>
     <t>We propose and present a parallelized metric framework for evaluating human-machine teams that draws upon current knowledge of human-systems interfacing and integration but is rooted in team-centric concepts. Humans and machines working together as a team involves interactions that will only increase in complexity as machines become more intelligent, capable teammates. Assessing such teams will require explicit focus on not just the human-machine interfacing but the full spectrum of interactions between and among agents. As opposed to focusing on isolated qualities, capabilities, and performance contributions of individual team members, the proposed framework emphasizes the collective team as the fundamental unit of analysis and the interactions of the team as the key evaluation targets, with individual human and machine metrics still vital but secondary. With teammate interaction as the organizing diagnostic concept, the resulting framework arrives at a parallel assessment of the humans and machines, analyzing their individual capabilities less with respect to purely human or machine qualities and more through the prism of contributions to the team as a whole. This treatment reflects the increased machine capabilities and will allow for continued relevance as machines develop to exercise more authority and responsibility. This framework allows for identification of features specific to human-machine teaming that influence team performance and efficiency, and it provides a basis for operationalizing in specific scenarios. Potential applications of this research include test and evaluation of complex systems that rely on human-system interaction, including—though not limited to—autonomous vehicles, command and control systems, and pilot control systems.</t>
   </si>
   <si>
@@ -4185,9 +4125,6 @@
     <t>How many success-or-failure observations should we collect from a computer simulation? Often, researchers use space-filling design of experiments when planning modeling and simulation (M&amp;S) studies. We are not satisfied with existing guidance on justifying the number of runs when developing these designs, either because the guidance is insufficiently justified, does not provide an unambiguous answer, or is not based on optimizing a statistical measure of merit. Analysts should use confidence interval margin of error as the statistical measure of merit for M&amp;S studies intended to characterize overall M&amp;S behavioral trends. Unfortunately, the margin of error for studies involving factors and success-or-failure (or binary) outcomes requires knowing model parameters when using logistic regression. We explore how an upper bound on the margin of error, needing less information about the statistical model we need to estimate, can assist in sample size planning. While the upper bound needs further theoretical refinement, simulation studies suggest the upper bound may provide a means of justifying M&amp;S study sample sizes with a statistical measure of merit.</t>
   </si>
   <si>
-    <t>For these situations in which an empirically vetted scale does not exist or is not suitable, a custom scale may be created. This document presents a comprehensive process for establishing the defensible use of a custom scale. At the highest level, this process encompasses (1) establishing validity of the scale, (2) establishing reliability of the scale, and (3) assessing dimensionality, whether intended or unintended, of the scale. First, the concept of validity is described, including how validity may be established using operators and subject matter experts. The concept of scale reliability is described, with guidelines for computing, interpreting, and using results to inform potential modifications to a custom scale. Next, a method for investigating the dimensionality ofa scale, exploratory factor analysis, is described, along with a walkthrough of software implementation and results. Finally, confirmatory factor analysis, a technique for testing a priori hypotheses about dimensionality, is presented.</t>
-  </si>
-  <si>
     <t xml:space="preserve"> As operational testing becomes increasingly integrated and research questions become more difficult to answer, IDA’s Test Science team has found Bayesian models to be powerful data analysis methods. Analysts and decision-makers should understand the differences between this approach and the conventional way of analyzing data. It is also important to recognize when an analysis could benefit from the inclusion of prior information—what we already know about a system’s performance—and to understand the proper way to incorporate that information. To apply Bayesian methods, analysts need to comprehend some technical aspects of this approach and know how to properly use appropriate statistical software. In this course, students learn the intuition behind Bayesian statistics, the mathematical details of posterior distributions, how to fit simple Bayesian models using computer software, and how to assess model fit.</t>
   </si>
   <si>
@@ -4275,9 +4212,6 @@
     <t>This presentation documents the work of IDA 2024 Summer Associate Emma Mitchell. The work presented details an R Shiny application developed to provide a user-friendly software tool for researchers to use in planning for and analyzing system reliability. Specifically, the presentation details how one can plan for a reliability test using Bayesian Reliability Assurance test methods. Such tests utilize supplementary data and information, including reliability models, prior test results, expert judgment, and knowledge of environmental conditions, to plan for reliability testing, which in turn can often help in reducing the required amount of testing. In the planning phase, the application enables researchers to use Bayesian methods to incorporate supplementary data when determining appropriate test lengths. In the analysis phase, the tool allows researchers to combine information through Bayesian methods, resulting in better uncertainty quantification than traditional methods.</t>
   </si>
   <si>
-    <t>Bayesian Design, Generalized Linear Models, Optimal Design, Response Surface Methods</t>
-  </si>
-  <si>
     <t>Experimental Design, Wind Tunnel Testing, Monte Carlo</t>
   </si>
   <si>
@@ -4287,12 +4221,6 @@
     <t>Factorial Design, Optimal Design, Power, Response Surface Methodology, Space-Filling Design, Test And Evaluation</t>
   </si>
   <si>
-    <t>Computer Simulation, Gaussian Process Models, Integrated Variance, Space-Filling Designs</t>
-  </si>
-  <si>
-    <t>M&amp;S, Verification And Validation, Accreditation</t>
-  </si>
-  <si>
     <t>Uncertainty Quantification, Data Analysis</t>
   </si>
   <si>
@@ -4311,51 +4239,27 @@
     <t>Survey, Dimension Reduction, Reliability, Scale Validity</t>
   </si>
   <si>
-    <t>Reliability, Exponential Distribution, Parameter, Hazard Function, Failure Rate, Confidence Bound, Normal Distribution, Weibull Distribution</t>
-  </si>
-  <si>
     <t>Observational Studies</t>
   </si>
   <si>
     <t>Complex System Reliability, Experimental Design, Reliability Experiments, Restricted Randomization, Power Analysis</t>
   </si>
   <si>
-    <t>Mixed Effect Models, Multi Level Models, Sample Size, Effect Size, Power</t>
-  </si>
-  <si>
     <t>Reproducible Analyses</t>
   </si>
   <si>
-    <t>Statistics, Descriptive Statistics, Inferential Statistics, Graphics, Non-Parametrics Statistics</t>
-  </si>
-  <si>
     <t>Data Visualization, Statistics</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>Interviews, Qualitative Coding, Qualitative Data</t>
-  </si>
-  <si>
     <t>Git, Reproducible Research, Reproducible Analyses, Data Management, Tutorial</t>
   </si>
   <si>
-    <t>Bayesian Analysis, Reliability Analysis, Test Planning</t>
-  </si>
-  <si>
-    <t>Design Thinking, Operational Testing, Operational Test Design</t>
-  </si>
-  <si>
-    <t>Operational Testing, Logistic Regression, Statistical Power, Signal-To-Noise Ratio, Monte Carlo</t>
-  </si>
-  <si>
     <t>Mixed Effects Models</t>
   </si>
   <si>
-    <t>I-Optimal Design, Chemical Agent Detector, Response Surface Modeling</t>
-  </si>
-  <si>
     <t>Personal Protective Equipment, Combat Helmets, Statistical Analyses</t>
   </si>
   <si>
@@ -4368,36 +4272,12 @@
     <t>Design of Experiments, Experimental Protocol, Experimental Strategy, Scientific Method, Sequential Experimentation</t>
   </si>
   <si>
-    <t>Bayesian, Reliability, Paladin, Sequence of Models, Experimental Design</t>
-  </si>
-  <si>
     <t>Design of Experiments, Sample Size Determination, Hypothesis Testing, Statistical Power, Type III Error, Unified Effect Size</t>
   </si>
   <si>
-    <t xml:space="preserve"> Defense Testing, Developmental Testing, DOD, Military Defense, U.S. Military</t>
-  </si>
-  <si>
-    <t>JMP Software, Statistics, Operational Testing, Design of Experiments</t>
-  </si>
-  <si>
     <t>Data Science, Statistics, Uncertainty Quantification, Reform Test and Evaluation</t>
   </si>
   <si>
-    <t>Artificial Intelligence,  Test and Evaluation,  Human-System Integration</t>
-  </si>
-  <si>
-    <t>Computer Experiments, Design f Experiments, Model Assessment and Validation, Uncertainty Quantification</t>
-  </si>
-  <si>
-    <t>Trust In Automated Systems Test (TOAST), Autonomy, Trust in Automation</t>
-  </si>
-  <si>
-    <t>Mixed Effect Models, Multi Level Models, Uncertainty Quantification, R</t>
-  </si>
-  <si>
-    <t>Operational Testing, Design of Experiments, Statistics</t>
-  </si>
-  <si>
     <t>Survey Administration Tool, Survey Management, Survey Design and Analysis</t>
   </si>
   <si>
@@ -4410,148 +4290,262 @@
     <t>Circular Error Probable, Department of Defense, Design of Experiments, Statistical Modeling</t>
   </si>
   <si>
-    <t>Test Evaluation Verification and Validation (TEV&amp;V), Artificial Intelligence (AI), Joint Artificial Intelligence Center (JAIC), Artificial Intelligence Enhanced Autonomous Capabilities, Autonomy Framework</t>
-  </si>
-  <si>
-    <t>Artificial Intelligence, Autonomous Systems, Autonomy, Machine Learning, Military AI, T&amp;E, Test &amp; Evaluation, Test Methods, Test Strategy, Test Evaluation Verification and Validation (TEV&amp;V), TEV&amp;V</t>
-  </si>
-  <si>
-    <t>TARTA, Test Evaluation Verification and Validation, Autonomous Systems, Artificial Intelligence (AI), AI, Autonomy Framework</t>
-  </si>
-  <si>
-    <t>Design of Experiments, Gaussian Process Modeling, Modeling &amp; Simulation, Space-Filling Designs, Statistics</t>
-  </si>
-  <si>
-    <t>Bayesian Statistics, Energy Statistics, Live Fire Test and Evaluation, Modeling and Simulation, M&amp;S</t>
-  </si>
-  <si>
     <t>Design of Experiments, Sample Size Determination, Sequential Probability Ratio Test, Statistical Power</t>
   </si>
   <si>
-    <t>Gaussian Process Modeling, Generalized Additive Models, Modeling and Simulation Validation, Simulation, Statistical Methods</t>
-  </si>
-  <si>
-    <t>Automated System, Autonomous, Reliance, Trust, Trust In Automated Systems Test (TOAST)</t>
-  </si>
-  <si>
     <t>Simulation, Statistics, Data Science, Modeling, Best Practices</t>
   </si>
   <si>
-    <t>Survey, System Usability Scale (SUS), Reliability, Logistic Regression, Binary Response, Likert Response, Interactive Web Application, Reproducibility, Shiny</t>
-  </si>
-  <si>
-    <t>Artificial Intelligence (AI), AI, Human-Machine Teaming, Metrics For Human-Machine Teams, Topological Model</t>
-  </si>
-  <si>
-    <t>Modeling and Simulation (M&amp;S) Validation, M&amp;S, Statistical Analysis, Wald Test, Weapons Analysis Facility</t>
-  </si>
-  <si>
     <t>JMP, Space Filling Design, R, Design of Experiments, Modeling and Simulation</t>
   </si>
   <si>
-    <t>Modeling and Simulation Validation, M&amp;S, Statistical Methods, Design of Experiments, Operational Testing</t>
-  </si>
-  <si>
-    <t>Armored Multi-Purpose Vehicle (AMPV), Full-Up System Level (FUSL), Ground Combat Vehicle (GCV), Modeling and Simulation (M&amp;S) Validation, Statistical Analysis, Verification Validation and Accreditation (VV&amp;A), Vulnerability Assessment</t>
-  </si>
-  <si>
-    <t>Statistics, Modeling and Simulation, M&amp;S, Verification Validation and Accreditation</t>
-  </si>
-  <si>
     <t>Functional Data Analysis, Hypothesis Testing, Confidence Intervals, Simultaneous Confidence Intervals, Fishers Combined Probability Test, Modeling and Simulation Validation, Radar Tracks, Functional Principal Component Analysis</t>
   </si>
   <si>
-    <t>Operational Test and Evaluation, Statistical Methods, Modeling and Simulation, Federated Models, Federated M&amp;S</t>
-  </si>
-  <si>
     <t>Validation, Verification, Uncertainty Quantification, Live Fire Test and Evaluation, Vulnerability Assessment, Design of Experiments, Propagation of Uncertainty</t>
   </si>
   <si>
-    <t>Censored Data Analysis, Naval Surface Gunnery, Continuous Response</t>
-  </si>
-  <si>
-    <t>Operational Test, Design of Experiments, Problem Discovery, Naval Postgraduate School, Value of Operational Testing, Test and Evaluation</t>
-  </si>
-  <si>
     <t>Generalized Linear Models, Design of Experiments, Signal-To-Noise Ratio, Test Adequacy</t>
   </si>
   <si>
     <t>System Evaluation, Verification and Validation, Missile Simulation</t>
   </si>
   <si>
-    <t>AH-64E Apache Attack Helicopter, KMI, WIN-T, Warfighter Information Network-Tactical, Key Management, Lessons Learned, Reliability, CVN-78, THAAD (Theater High Altitude Area Defense), Joint Strike Fighter, Best Practices</t>
-  </si>
-  <si>
     <t>Design of Experiments, Nonlinear Mixed Model, Regression With Lifetime Data, Weibull Distribution</t>
   </si>
   <si>
     <t>Test and Evaluation, Measures of Effectiveness</t>
   </si>
   <si>
-    <t>Bayesian Analysis, Test Planning, Scientific Test and Analysis Techniques</t>
-  </si>
-  <si>
     <t>Design of Experiments, Statistical Analyses, Test Planning, Statistical Measures of Merit</t>
   </si>
   <si>
     <t>Defense Acquisition, Design of Experiments, Experimental Methods</t>
   </si>
   <si>
-    <t>Air Force, Pilot Training Next (PTN), Simulators, Pilot Training, Linear Mixed Models</t>
-  </si>
-  <si>
     <t>Leadership Perspective, Science of Test Workshop, Statistics</t>
   </si>
   <si>
-    <t>HSI, Human-Systems, Human Factors, Operational, DOE, Analysis, Suitability, Usability, Workload, Training, Trust, Situational Awareness, Survey, Behavior, Interview, Focus Group, Qualitative, Quantitative, Mixed-Methods, Triangulation, Validated Scale</t>
-  </si>
-  <si>
     <t>A-Optimality, Constrained Region Of Experimentation, D-Optimality, Design of Experiments, Factorial Experiments, G-Optimality, I-Optimality, Response Surfaces</t>
   </si>
   <si>
-    <t>Hybrid Design, M&amp;S, Computer Simulation, Design of Experiments</t>
-  </si>
-  <si>
     <t>Department Of Defense, Sequential Design, Design of Experiments, Ballistic Resistance Testing, Three-Phase Optimal Design</t>
   </si>
   <si>
     <t>Power Analysis, Design of Experiments, JMP, Design Expert</t>
   </si>
   <si>
-    <t>Design of Experiments, Observational Studies, Survey Design and Analysis, Statistical Analysis, Defense Acquisition University (DAU)</t>
-  </si>
-  <si>
-    <t>Design of Experiments, Statistical Analyses, Test Planning, Censored Data, Binomial</t>
-  </si>
-  <si>
-    <t>Training, Survey, Survey Development, Survey Validation, Human System Interaction (HSI)</t>
-  </si>
-  <si>
-    <t>Situation Awareness (SA), Human System Interaction (HSI), Meta-Analysis, Teams, Assessment Methodology</t>
-  </si>
-  <si>
-    <t>Artificial Intelligence, Data Fusion, Data Integration, Test Concept, Human System Interaction (HSI)</t>
-  </si>
-  <si>
-    <t>Survey Methods, Human System Interaction (HSI), Test Design, Statistics, Sample Size</t>
-  </si>
-  <si>
-    <t>HSI, Human System Interaction, Human Factors, DOE, Analysis, Suitability, Usability, Workload, Training, Trust, Situational Awareness, Survey, Behavior, Interview, Focus Group, Qualitative, Quantitative, Mixed-Methods, Triangulation, Validated Scale</t>
-  </si>
-  <si>
     <t>Surveys, Operational Test and Evaluation, Human System Interaction</t>
   </si>
   <si>
     <t>Agent, Artificial Intelligence, Human-Machine Team, Human System Interaction, Metrics, AI</t>
   </si>
   <si>
-    <t xml:space="preserve">Artificial Intellgience,  AI, Test And Evaluation,  Human System Interaction (HSI) </t>
-  </si>
-  <si>
-    <t>Human System Interaction, Human-Machine Teaming, Trust, Trustworthiness, AI, Behavioral Measures</t>
-  </si>
-  <si>
-    <t>Human System Interaction (HSI), Human-Machine Teaming, Behavioral Measures</t>
+    <t>Statistics, Descriptive Statistics, Inferential Statistics, Graphics, Non-Parametric Statistics</t>
+  </si>
+  <si>
+    <t>The areas of application for design of experiments principles have evolved, mimicking the growth of U.S. industries over the last century, from agriculture to manufacturing to chemical and process industries to the services and government sectors. In addition, statistically based quality programs adopted by businesses morphed from total quality management to Six Sigma and, most recently, statistical engineering (see Hoerl and Snee 2010). The good news about these transformations is that each evolution contains more technical substance, embedding the methodologies as core competencies, and is less of a ‘‘program.’’ Design of experiments is fundamental to statistical engineering and is receiving increased attention within large government agencies such as the National Aeronautics and Space Administration (NASA) and the Department of Defense. Because test policy is intended to shape test programs, numerous test agencies have experimented with policy wording since about 2001. The Director of Operational Test &amp; Evaluation has recently (2010) published guidelines to mold test programs into a sequence of well-designed and statistically defensible experiments. Specifically, the guidelines require, for the first time, that test programs report statistical power as one proof of sound test design. This article presents the underlying tenets of design of experiments, as applied in the Department of Defense, focusing on factorial, fractional factorial, and response surface design and analyses. The concepts of statistical modeling and sequential experimentation are also emphasized. Military applications are presented for testing and evaluation of weapon system acquisition, including force-on-force tactics, weapons employment and maritime search, identification, and intercept.</t>
+  </si>
+  <si>
+    <t>Reliability is an essential element in assessing the operational suitability of Department of Defense weapon systems. Reliability takes a prominent role in both the design and analysis of operational tests. In the current era of reduced budgets and increased reliability requirements, it is challenging to verify reliability requirements in a single test. Furthermore, all available data should be considered in order to ensure evaluations provide the most appropriate analysis of the system’s reliability. This paper describes the benefits of using parametric statistical models to combine information across multiple testing events. Both frequentist and Bayesian inference techniques are employed and they are compared and contrasted to illustrate different statistical methods for combining information. We apply these methods to data collected during the developmental and operational test phases for the Stryker family of vehicles. We show that, when we combine the available information across two test phases for the Stryker family of vehicles, reliability estimates are more accurate and precise than those reported previously using traditional methods that use only operational test data in their reliability assessments.</t>
+  </si>
+  <si>
+    <t>Thomas, Dean, and Rebecca Dickinson. “Validating the Probability of Raid Annihilation Testbed Using a Statistical Approach.” The ITEA Journal of Test and Evaluation 36, no. 2 (June 2015).</t>
+  </si>
+  <si>
+    <t>Alyson Wilson, Kassandra Fronczyk</t>
+  </si>
+  <si>
+    <t>For situations in which an empirically vetted scale does not exist or is not suitable, a custom scale may be created. This document presents a comprehensive process for establishing the defensible use of a custom scale. At the highest level, this process encompasses (1) establishing validity of the scale, (2) establishing reliability of the scale, and (3) assessing dimensionality, whether intended or unintended, of the scale. First, the concept of validity is described, including how validity may be established using operators and subject matter experts. The concept of scale reliability is described, with guidelines for computing, interpreting, and using results to inform potential modifications to a custom scale. Next, a method for investigating the dimensionality of a scale, exploratory factor analysis, is described, along with a walkthrough of software implementation and results. Finally, confirmatory factor analysis, a technique for testing a priori hypotheses about dimensionality, is presented.</t>
+  </si>
+  <si>
+    <t>Reliability tests determine which factors drive system reliability. Often, the reliability or failure time data collected in these tests tend to follow distinctly non- normal distributions and include censored observations. The experimental design should accommodate the skewed nature of the response and allow for censored observations, which occur when systems under test do not fail within the allotted test time. To account for these design and analysis considerations, Monte Carlo simulations are frequently used to evaluate experimental design properties. Simulation provides accurate power calculations as a function of sample size, allowing researchers to determine adequate sample sizes at each level of the treatment. However, simulation may be inefficient for comparing multiple experiments of various sizes. In this document, we present a closed form approach for calculating power, based on the non- central chi-squared approximation to the distribution of the likelihood ratio statistic. The solution can be used to compare multiple designs and accommodate trade-space analyses between power, effect size, model formulation, sample size, censoring rates, and design type. To demonstrate the efficiency of our approach, we provide a comparison to estimates that are generated using Monte Carlo simulation.</t>
+  </si>
+  <si>
+    <t>A presentation on the theory and practice of observational studies.  Specific average treatment effect methods include matching, difference-in-difference estimators, and instrumental variables.</t>
+  </si>
+  <si>
+    <t>Wojton, Heather, Kelly Avery, Laura Freeman, and Thomas Johnson. “Designing Experiments for Model Validation – The Foundations for Uncertainty Quantification.” The  ITEA Journal of Test and Evaluation 40, no. 1 (2019).</t>
+  </si>
+  <si>
+    <t>could link to the  ITEA Journal of Test and Evaluation paper.</t>
+  </si>
+  <si>
+    <t>Medlin, Rebecca, and Andrew Flack. “Managing T&amp;E Data to Encourage Reuse.” The  ITEA Journal of Test and Evaluation of Test and Evaluation, 2019.</t>
+  </si>
+  <si>
+    <t>The  ITEA Journal of Test and Evaluation</t>
+  </si>
+  <si>
+    <t>In the acquisition and testing world, data analysts repeatedly encounter certain categories of data, such as time or distance until an event (e.g., failure, alert, detection), binary outcomes (e.g., success/failure, hit/miss), and survey responses. Analysts need tools that enable them to produce quality and timely analyses of the data they acquire during testing. This poster presents four web-based apps that can analyze these types of data. The apps are designed to assist analysts and researchers with simple repeatable analysis tasks, such as building summary tables and plots for reports or briefings. Using software tools like these apps can increase reproducibility of results, timeliness of analysis and reporting, attractiveness and standardization of aesthetics in figures, and accuracy of results. The first app models reliability of a system or component by fitting parametric statistical distributions to time-to-failure data. The second app fits a logistic regression model to binary data with one or two independent continuous variables as The third calculates summary statistics and produces plots of groups of Likert-scale survey question responses. The fourth calculates the system usability scale (SUS) scores for SUS survey responses and enables the app user to plot scores versus an independent variable. These apps are available for public use on the Test Science Interactive Tools webpage https://testscience.org/interactive-tools/.</t>
+  </si>
+  <si>
+    <t>Training, Survey, Survey Development, Survey Validation, Human System Interaction</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence, Data Fusion, Data Integration, Test Concept, Human System Interaction</t>
+  </si>
+  <si>
+    <t>Survey Methods, Human System Interaction, Test Design, Statistics, Sample Size</t>
+  </si>
+  <si>
+    <t>Human System Interaction, Human-Machine Teaming, Behavioral Measures</t>
+  </si>
+  <si>
+    <t>TARTA, Test Evaluation Verification and Validation, Autonomy, Artificial Intelligence, AI, Autonomy Framework</t>
+  </si>
+  <si>
+    <t>Bayesian, Test Planning, Scientific Test and Analysis Techniques</t>
+  </si>
+  <si>
+    <t>Censored Data, Naval Surface Gunnery, Continuous Response</t>
+  </si>
+  <si>
+    <t>Reliability, Exponential Distribution, Parameter, Hazard Function, Failure Rate, Confidence Intervals, Normal Distribution, Weibull Distribution</t>
+  </si>
+  <si>
+    <t>Gaussian Process Model, Generalized Additive Models, Modeling and Simulation Validation, Simulation, Statistical Methods</t>
+  </si>
+  <si>
+    <t>Computer Simulation, Gaussian Process Model, Integrated Variance, Space-Filling Designs</t>
+  </si>
+  <si>
+    <t>Human Systems Interaction, Human System Interaction, Human Factors, Design of Experiments, Analysis, Suitability, Usability, Workload, Training, Trust, Situational Awareness, Survey, Behavior, Interview, Focus Group, Qualitative, Quantitative, Mixed-Methods, Triangulation, Validated Scale</t>
+  </si>
+  <si>
+    <t>Human Systems Interaction, Human Systems Interaction, Human Factors, Operational, Design of Experiments, Analysis, Suitability, Usability, Workload, Training, Trust, Situational Awareness, Survey, Behavior, Interview, Focus Group, Qualitative, Quantitative, Mixed-Methods, Triangulation, Validated Scale</t>
+  </si>
+  <si>
+    <t>Interview, Qualitative Coding, Qualitative Data</t>
+  </si>
+  <si>
+    <t>Hybrid Design, Modeling and Simulation, Computer Simulation, Design of Experiments</t>
+  </si>
+  <si>
+    <t>Modeling and Simulation, Verification And Validation, Accreditation</t>
+  </si>
+  <si>
+    <t>Statistics, Modeling and Simulation, Modeling and Simulation, Verification Validation and Accreditation</t>
+  </si>
+  <si>
+    <t>Operational Test and Evaluation, Statistical Methods, Modeling and Simulation, Federated Models, Federated Modeling and Simulation</t>
+  </si>
+  <si>
+    <t>JMP Software, Statistics, Operational Test and Evaluation, Design of Experiments</t>
+  </si>
+  <si>
+    <t>Statistics, Operational Test and Evaluation, Design of Experiments, Modeling and Simulation, Validation</t>
+  </si>
+  <si>
+    <t>Operational Test and Evaluation, Design of Experiments, Statistics</t>
+  </si>
+  <si>
+    <t>Design of Experiments, Operational Test and Evaluation, Statistics</t>
+  </si>
+  <si>
+    <t>Modeling and Simulation Validation, Modeling and Simulation, Statistical Methods, Design of Experiments, Operational Test and Evaluation</t>
+  </si>
+  <si>
+    <t>Design Thinking, Operational Test and Evaluation, Operational Test Design</t>
+  </si>
+  <si>
+    <t>Operational Test and Evaluation, Logistic Regression, Statistical Power, Signal-To-Noise Ratio, Monte Carlo</t>
+  </si>
+  <si>
+    <t>Operational Test, Design of Experiments, Problem Discovery, Naval Postgraduate School, Value of Operational Test and Evaluation, Test and Evaluation</t>
+  </si>
+  <si>
+    <t>Operational Test and Evaluation, Design of Experiments, Live Fire Test and Evaluation, Sequential Design, Sensitivity Testing</t>
+  </si>
+  <si>
+    <t>Air Force, Pilot Training Next , Simulators, Pilot Training, Linear Mixed Models</t>
+  </si>
+  <si>
+    <t>Bayesian, Reliability, Test Planning</t>
+  </si>
+  <si>
+    <t>Department of Defense, Reliability, Reliability Growth, Reliability, Test and Evaluation Master Plan</t>
+  </si>
+  <si>
+    <t>Bayesian Design, Generalized Linear Models, Optimal Design, Response Surface Methodology</t>
+  </si>
+  <si>
+    <t>I-Optimal Design, Chemical Agent Detector, Response Surface Methodology</t>
+  </si>
+  <si>
+    <t>Situation Awareness , Human System Interaction, Meta-Analysis, Teams, Assessment Methodology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Design of Experiments, Observational Studies, Survey Design and Analysis, Statistical Analyses, Defense Acquisition University </t>
+  </si>
+  <si>
+    <t>Design of Experiments, Operational Test and Evaluation, Statistical Analyses</t>
+  </si>
+  <si>
+    <t>Survey, System Usability Scale , Reliability, Logistic Regression, Binary Response, Likert Response, Interactive Web Application, Reproducibility, Shiny</t>
+  </si>
+  <si>
+    <t>AH-64E Apache Attack Helicopter, KMI, , Warfighter Information Network-Tactical, Key Management, Lessons Learned, Reliability, CVN-78, THAAD (Theater High Altitude Area Defense), Joint Strike Fighter, Best Practices</t>
+  </si>
+  <si>
+    <t>Bayesian, Reliability, Paladin, Sequence of Models, Design of Experiments</t>
+  </si>
+  <si>
+    <t>Defense, Operational Test and Evaluation, Design of Experiments, Modeling and Simulation</t>
+  </si>
+  <si>
+    <t>Defense Testing, Developmental Testing, DOD, Military Defense, U.S. Military</t>
+  </si>
+  <si>
+    <t>TOAST, Autonomy, Trust in Automation</t>
+  </si>
+  <si>
+    <t>Mixed Effects Models, Multi-level Models, Sample Size, Effect Size, Power</t>
+  </si>
+  <si>
+    <t>Mixed Effects Models, Multi-level Models, Uncertainty Quantification, R</t>
+  </si>
+  <si>
+    <t>Test Evaluation Verification and Validation , Artificial Intelligence, Joint Artificial Intelligence Center, Artificial Intelligence Enhanced Autonomous Capabilities, Autonomy Framework</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence, Autonomy, Machine Learning, Military AI, Test and Evaluation, Test Methods, Test Strategy, Test Evaluation Verification and Validation</t>
+  </si>
+  <si>
+    <t>Modeling and Simulation Validation, Torpedo, Design of Experiments, Undersea Warfare</t>
+  </si>
+  <si>
+    <t>Design of Experiments, Gaussian Process Model, Modeling and Simulation, Space-Filling Designs, Statistics</t>
+  </si>
+  <si>
+    <t>Bayesian Statistics, Energy Statistics, Live Fire Test and Evaluation, Modeling and Simulation</t>
+  </si>
+  <si>
+    <t>Autonomy, Autonomous, Reliance, Trust, TOAST</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence, Human-Machine Teaming, Metrics For Human-Machine Teams, Topological Model</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence, Test and Evaluation, Human System Interaction</t>
+  </si>
+  <si>
+    <t>Modeling and Simulation Validation, Modeling and Simulation, Statistical Analyses, Wald Test, Weapons Analysis Facility</t>
+  </si>
+  <si>
+    <t>Armored Multi-Purpose Vehicle (AMPV), Full-Up System Level , Ground Combat Vehicle (GCV), Modeling and Simulation Validation, Statistical Analyses, Verification Validation and Accreditation , Vulnerability Assessment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Artificial Intelligence, Test And Evaluation, Human System Interaction </t>
+  </si>
+  <si>
+    <t>Human System Interaction, Human-Machine Teaming, Trust, Trustworthiness, Artificial Intelligence, Behavioral Measures</t>
+  </si>
+  <si>
+    <t>Design of Experiments, Statistical Analyses, Test Planning, Censored Data, Binomial Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Space-Filling Designs are a common choice of experimental design strategy for computer experiments. This paper compares space filling design types based on their theoretical prediction variance properties with respect to the Gaussian Process model. </t>
   </si>
 </sst>
 </file>
@@ -4994,57 +4988,57 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7078B797-123B-4556-84D1-DEC1D433D8DE}">
   <dimension ref="A1:S131"/>
-  <sheetFormatPr defaultColWidth="27.88671875" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="27.84375" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="13.6640625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="8.21875" style="16" customWidth="1"/>
-    <col min="3" max="3" width="26.5546875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="39.21875" style="7" customWidth="1"/>
+    <col min="1" max="1" width="13.69140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="8.23046875" style="16" customWidth="1"/>
+    <col min="3" max="3" width="26.53515625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="39.23046875" style="7" customWidth="1"/>
     <col min="5" max="5" width="42" style="7" customWidth="1"/>
-    <col min="6" max="6" width="31.44140625" style="2" customWidth="1"/>
-    <col min="7" max="13" width="27.88671875" style="2"/>
-    <col min="14" max="14" width="52.88671875" style="2" customWidth="1"/>
-    <col min="15" max="15" width="50.88671875" style="2" customWidth="1"/>
-    <col min="16" max="16" width="17.5546875" style="2" customWidth="1"/>
-    <col min="17" max="16384" width="27.88671875" style="2"/>
+    <col min="6" max="6" width="31.4609375" style="2" customWidth="1"/>
+    <col min="7" max="13" width="27.84375" style="2"/>
+    <col min="14" max="14" width="52.84375" style="2" customWidth="1"/>
+    <col min="15" max="15" width="50.84375" style="2" customWidth="1"/>
+    <col min="16" max="16" width="17.53515625" style="2" customWidth="1"/>
+    <col min="17" max="16384" width="27.84375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B1" s="15" t="s">
         <v>9</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="D1" s="8" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>506</v>
+        <v>495</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>579</v>
+        <v>564</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>769</v>
+        <v>748</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>770</v>
+        <v>749</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>771</v>
+        <v>750</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>3</v>
@@ -5056,36 +5050,36 @@
         <v>19</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="R1" s="1" t="s">
         <v>16</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B2" s="16">
         <v>2009</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>46</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>507</v>
+        <v>496</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>47</v>
@@ -5095,96 +5089,96 @@
         <v>48</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>788</v>
+        <v>852</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B3" s="16">
         <v>2009</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="D3" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>497</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>67</v>
-      </c>
-      <c r="E3" s="12" t="s">
-        <v>508</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>539</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>68</v>
       </c>
       <c r="H3" s="3"/>
       <c r="N3" s="2" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>790</v>
+        <v>768</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B4" s="16">
         <v>2010</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>509</v>
+        <v>498</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>539</v>
+        <v>524</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H4" s="3"/>
       <c r="N4" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>789</v>
+        <v>767</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="2" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B5" s="16">
         <v>2011</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>510</v>
+        <v>499</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>28</v>
@@ -5194,171 +5188,171 @@
         <v>27</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>865</v>
+        <v>805</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="R5" s="2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="2" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="B6" s="16">
         <v>2011</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>511</v>
+        <v>500</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>573</v>
+        <v>558</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="L6" s="3"/>
       <c r="N6" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>866</v>
+        <v>836</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="2" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B7" s="16">
         <v>2012</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="D7" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>501</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>63</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>512</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>64</v>
       </c>
       <c r="H7" s="3"/>
       <c r="N7" s="2" t="s">
-        <v>319</v>
+        <v>811</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>791</v>
+        <v>769</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="R7" s="2" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B8" s="16">
         <v>2013</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>729</v>
+        <v>711</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>52</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>513</v>
+        <v>502</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>53</v>
       </c>
       <c r="H8" s="3"/>
       <c r="N8" s="2" t="s">
-        <v>54</v>
+        <v>878</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>792</v>
+        <v>832</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="R8" s="2" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="2" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B9" s="16">
         <v>2013</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>514</v>
+        <v>503</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="H9" s="3"/>
       <c r="N9" s="5" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>818</v>
+        <v>786</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="2" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B10" s="16">
         <v>2014</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>7</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>515</v>
+        <v>504</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>6</v>
@@ -5368,46 +5362,46 @@
         <v>8</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>867</v>
+        <v>806</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="2" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B11" s="16">
         <v>2014</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>516</v>
+        <v>505</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>542</v>
+        <v>527</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H11" s="3"/>
       <c r="N11" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>868</v>
+        <v>807</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="2" t="s">
         <v>36</v>
       </c>
@@ -5415,32 +5409,32 @@
         <v>2015</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="D12" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>556</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>87</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>571</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>88</v>
       </c>
       <c r="H12" s="3"/>
       <c r="N12" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>730</v>
+        <v>712</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="2" t="s">
         <v>36</v>
       </c>
@@ -5448,151 +5442,151 @@
         <v>2015</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="D13" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="E13" s="13" t="s">
+        <v>506</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="G13" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="E13" s="13" t="s">
-        <v>517</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>133</v>
-      </c>
       <c r="K13" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="L13" s="3"/>
       <c r="N13" s="2" t="s">
-        <v>441</v>
+        <v>812</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="2" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="B14" s="16">
         <v>2015</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>530</v>
+        <v>813</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="H14" s="3"/>
       <c r="N14" s="2" t="s">
-        <v>442</v>
+        <v>431</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="2" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="B15" s="16">
         <v>2015</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>518</v>
+        <v>507</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>542</v>
+        <v>527</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="L15" s="3"/>
       <c r="N15" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>819</v>
+        <v>859</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="2" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="B16" s="16">
         <v>2015</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>594</v>
+        <v>578</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>542</v>
+        <v>527</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="L16" s="3"/>
       <c r="N16" s="2" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>793</v>
+        <v>837</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="2" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="B17" s="16">
         <v>2016</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>595</v>
+        <v>579</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>542</v>
+        <v>527</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>11</v>
@@ -5602,13 +5596,13 @@
         <v>12</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>794</v>
+        <v>770</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="2" t="s">
         <v>36</v>
       </c>
@@ -5616,16 +5610,16 @@
         <v>2016</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>365</v>
+        <v>814</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>519</v>
+        <v>508</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>35</v>
@@ -5635,33 +5629,33 @@
         <v>34</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>795</v>
+        <v>771</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="R18" s="2" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="2" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="B19" s="16">
         <v>2016</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>596</v>
+        <v>580</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="K19" s="3" t="s">
         <v>43</v>
@@ -5674,60 +5668,60 @@
         <v>36</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="2" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B20" s="16">
         <v>2016</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="D20" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="E20" s="12" t="s">
+        <v>548</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="G20" s="3" t="s">
         <v>122</v>
-      </c>
-      <c r="E20" s="12" t="s">
-        <v>563</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>539</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>123</v>
       </c>
       <c r="H20" s="3"/>
       <c r="N20" s="2" t="s">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>796</v>
+        <v>772</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="2" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="B21" s="16">
         <v>2017</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="D21" s="14" t="s">
         <v>13</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>597</v>
+        <v>581</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>542</v>
+        <v>527</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>14</v>
@@ -5739,1072 +5733,1072 @@
         <v>15</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>797</v>
+        <v>773</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="R21" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="22" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="2" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B22" s="16">
         <v>2017</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>520</v>
+        <v>509</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H22" s="3"/>
       <c r="K22" s="2" t="s">
-        <v>450</v>
+        <v>439</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>820</v>
+        <v>787</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="2" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B23" s="16">
         <v>2017</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="D23" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="E23" s="12" t="s">
+        <v>510</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="G23" s="3" t="s">
         <v>127</v>
-      </c>
-      <c r="E23" s="12" t="s">
-        <v>521</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>598</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>128</v>
       </c>
       <c r="H23" s="3"/>
       <c r="N23" s="2" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>130</v>
+        <v>860</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="R23" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="2" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="B24" s="16">
         <v>2017</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>599</v>
+        <v>583</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>542</v>
+        <v>527</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>798</v>
+        <v>774</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="2" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B25" s="16">
         <v>2018</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="D25" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>511</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="G25" s="3" t="s">
         <v>92</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>522</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>93</v>
       </c>
       <c r="H25" s="3"/>
       <c r="N25" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>821</v>
+        <v>861</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="2" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="B26" s="16">
         <v>2018</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>600</v>
+        <v>584</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>542</v>
+        <v>527</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="L26" s="3"/>
       <c r="N26" s="2" t="s">
-        <v>758</v>
+        <v>815</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>799</v>
+        <v>775</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B27" s="16">
         <v>2018</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>523</v>
+        <v>512</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="H27" s="3"/>
       <c r="N27" s="2" t="s">
-        <v>443</v>
+        <v>432</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>800</v>
+        <v>830</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B28" s="16">
         <v>2018</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>564</v>
+        <v>549</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>539</v>
+        <v>524</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>565</v>
+        <v>550</v>
       </c>
       <c r="H28" s="3"/>
       <c r="K28" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="L28" s="3"/>
       <c r="N28" s="2" t="s">
-        <v>323</v>
+        <v>816</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>454</v>
+        <v>443</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="2" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B29" s="16">
         <v>2018</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>601</v>
+        <v>585</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>542</v>
+        <v>527</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H29" s="3"/>
       <c r="N29" s="2" t="s">
-        <v>754</v>
+        <v>734</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>822</v>
+        <v>840</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="30" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="2" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="B30" s="16">
         <v>2018</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>602</v>
+        <v>586</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>542</v>
+        <v>527</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>257</v>
+        <v>841</v>
       </c>
       <c r="P30" s="2" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="31" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="2" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="B31" s="16">
         <v>2018</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>603</v>
+        <v>587</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="H31" s="3"/>
       <c r="N31" s="2" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>823</v>
+        <v>788</v>
       </c>
       <c r="P31" s="2" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="2" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B32" s="16">
         <v>2018</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>604</v>
+        <v>588</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>542</v>
+        <v>527</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>439</v>
+        <v>429</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>731</v>
+        <v>817</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>801</v>
+        <v>776</v>
       </c>
       <c r="P32" s="2" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="33" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="2" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="B33" s="16">
         <v>2018</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>524</v>
+        <v>513</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>605</v>
+        <v>589</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>543</v>
+        <v>528</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L33" s="3"/>
       <c r="N33" s="2" t="s">
-        <v>732</v>
+        <v>713</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>869</v>
+        <v>855</v>
       </c>
       <c r="P33" s="2" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="34" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="2" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B34" s="16">
         <v>2019</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="D34" s="7" t="s">
         <v>44</v>
       </c>
       <c r="E34" s="12" t="s">
-        <v>525</v>
+        <v>514</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>45</v>
       </c>
       <c r="H34" s="3"/>
       <c r="N34" s="2" t="s">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>802</v>
+        <v>777</v>
       </c>
       <c r="P34" s="2" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="R34" s="2" t="s">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="35" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="2" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="B35" s="16">
         <v>2019</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>606</v>
+        <v>590</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>542</v>
+        <v>527</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="L35" s="3"/>
       <c r="N35" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>824</v>
+        <v>872</v>
       </c>
       <c r="P35" s="2" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="36" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="2" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="B36" s="16">
         <v>2019</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>531</v>
+        <v>818</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H36" s="3"/>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
       <c r="N36" s="2" t="s">
-        <v>733</v>
+        <v>714</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="P36" s="2" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="R36" s="2" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="37" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="2" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="B37" s="16">
         <v>2019</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>607</v>
+        <v>591</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>542</v>
+        <v>527</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H37" s="3"/>
       <c r="K37" s="6" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="L37" s="6"/>
       <c r="N37" s="2" t="s">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>825</v>
+        <v>65</v>
       </c>
       <c r="P37" s="2" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="R37" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="38" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="2" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="B38" s="16">
         <v>2019</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>526</v>
+        <v>515</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>527</v>
+        <v>516</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H38" s="3"/>
       <c r="K38" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="L38" s="3"/>
       <c r="M38" s="3" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="N38" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="O38" s="2" t="s">
+        <v>862</v>
+      </c>
+      <c r="P38" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="R38" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="O38" s="2" t="s">
-        <v>826</v>
-      </c>
-      <c r="P38" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="R38" s="2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="39" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="39" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="2" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="B39" s="16">
         <v>2019</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="D39" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>820</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="G39" s="3" t="s">
         <v>109</v>
-      </c>
-      <c r="E39" s="7" t="s">
-        <v>533</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>110</v>
       </c>
       <c r="H39" s="3"/>
       <c r="N39" s="2" t="s">
-        <v>734</v>
+        <v>715</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="P39" s="2" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="40" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="2" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B40" s="16">
         <v>2019</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>535</v>
+        <v>520</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>593</v>
+        <v>821</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H40" s="3"/>
       <c r="N40" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>803</v>
+        <v>863</v>
       </c>
       <c r="P40" s="2" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="41" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="2" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="B41" s="16">
         <v>2019</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>393</v>
+        <v>383</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>536</v>
+        <v>521</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>593</v>
+        <v>821</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H41" s="3"/>
       <c r="K41" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L41" s="3"/>
       <c r="N41" s="2" t="s">
-        <v>735</v>
+        <v>716</v>
       </c>
       <c r="O41" s="2" t="s">
-        <v>827</v>
+        <v>864</v>
       </c>
       <c r="P41" s="2" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="42" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="2" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="B42" s="16">
         <v>2019</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>388</v>
+        <v>378</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>608</v>
+        <v>592</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="K42" s="3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="L42" s="3"/>
       <c r="M42" s="6" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="O42" s="2" t="s">
-        <v>804</v>
+        <v>778</v>
       </c>
       <c r="P42" s="2" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="43" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="2" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="B43" s="16">
         <v>2019</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="D43" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="E43" s="11" t="s">
+        <v>593</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="K43" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="M43" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="N43" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="E43" s="11" t="s">
-        <v>609</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="K43" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="M43" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="N43" s="2" t="s">
-        <v>162</v>
-      </c>
       <c r="O43" s="2" t="s">
-        <v>805</v>
+        <v>810</v>
       </c>
       <c r="P43" s="2" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="44" spans="1:18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="B44" s="17">
         <v>2019</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>767</v>
+        <v>746</v>
       </c>
       <c r="D44" t="s">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>610</v>
+        <v>594</v>
       </c>
       <c r="F44" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="J44" s="2"/>
       <c r="K44" s="2"/>
       <c r="L44" s="2"/>
       <c r="N44" t="s">
-        <v>736</v>
+        <v>717</v>
       </c>
       <c r="O44" s="2" t="s">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="P44" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="45" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="2" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B45" s="16">
         <v>2019</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="E45" s="11" t="s">
-        <v>611</v>
+        <v>595</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="J45" s="3"/>
       <c r="N45" s="2" t="s">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="O45" s="2" t="s">
-        <v>455</v>
+        <v>444</v>
       </c>
       <c r="P45" s="2" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="46" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="2" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="B46" s="16">
         <v>2019</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E46" s="11" t="s">
-        <v>612</v>
+        <v>596</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J46" s="3"/>
       <c r="N46" s="2" t="s">
-        <v>737</v>
+        <v>718</v>
       </c>
       <c r="O46" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="P46" s="2" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="47" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" s="2" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B47" s="16">
         <v>2019</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E47" s="11" t="s">
-        <v>613</v>
+        <v>597</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>542</v>
+        <v>527</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H47" s="3"/>
       <c r="N47" s="2" t="s">
-        <v>738</v>
+        <v>719</v>
       </c>
       <c r="O47" s="2" t="s">
-        <v>828</v>
+        <v>842</v>
       </c>
       <c r="P47" s="2" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="48" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="2" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="B48" s="16">
         <v>2019</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E48" s="11" t="s">
-        <v>614</v>
+        <v>598</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="J48" s="3"/>
       <c r="N48" s="2" t="s">
-        <v>739</v>
+        <v>720</v>
       </c>
       <c r="O48" s="2" t="s">
-        <v>829</v>
+        <v>789</v>
       </c>
       <c r="P48" s="2" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="49" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="2" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B49" s="16">
         <v>2019</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E49" s="12" t="s">
-        <v>537</v>
+        <v>522</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="H49" s="3"/>
       <c r="N49" s="2" t="s">
-        <v>444</v>
+        <v>433</v>
       </c>
       <c r="O49" s="2" t="s">
-        <v>830</v>
+        <v>790</v>
       </c>
       <c r="P49" s="2" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="R49" s="3" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="50" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="2" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="B50" s="16">
         <v>2019</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>615</v>
+        <v>599</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>542</v>
+        <v>527</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="L50" s="3"/>
       <c r="N50" s="2" t="s">
-        <v>740</v>
+        <v>721</v>
       </c>
       <c r="O50" s="2" t="s">
-        <v>831</v>
+        <v>791</v>
       </c>
       <c r="P50" s="2" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="51" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" s="2" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B51" s="16">
         <v>2020</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>395</v>
+        <v>385</v>
       </c>
       <c r="D51" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E51" s="11" t="s">
-        <v>616</v>
+        <v>600</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>542</v>
+        <v>527</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>18</v>
       </c>
       <c r="H51" s="3"/>
       <c r="N51" s="2" t="s">
-        <v>741</v>
+        <v>722</v>
       </c>
       <c r="O51" s="2" t="s">
-        <v>258</v>
+        <v>843</v>
       </c>
       <c r="P51" s="2" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="52" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" s="2" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="B52" s="16">
         <v>2020</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>397</v>
+        <v>387</v>
       </c>
       <c r="D52" s="7" t="s">
         <v>49</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>539</v>
+        <v>524</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>50</v>
@@ -6815,215 +6809,215 @@
       </c>
       <c r="J52" s="3"/>
       <c r="K52" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="L52" s="3"/>
       <c r="N52" s="2" t="s">
-        <v>742</v>
+        <v>723</v>
       </c>
       <c r="O52" s="2" t="s">
-        <v>832</v>
+        <v>792</v>
       </c>
       <c r="P52" s="2" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="R52" s="2" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="53" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A53" s="2" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="B53" s="16">
         <v>2020</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="E53" s="11" t="s">
-        <v>617</v>
+        <v>601</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>542</v>
+        <v>527</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="H53" s="3"/>
       <c r="N53" s="2" t="s">
-        <v>743</v>
+        <v>724</v>
       </c>
       <c r="O53" s="2" t="s">
-        <v>833</v>
+        <v>865</v>
       </c>
       <c r="P53" s="2" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="54" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54" s="2" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="B54" s="16">
         <v>2020</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="E54" s="11" t="s">
-        <v>618</v>
+        <v>602</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>542</v>
+        <v>527</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="H54" s="3"/>
       <c r="K54" s="2" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>744</v>
+        <v>725</v>
       </c>
       <c r="O54" s="2" t="s">
-        <v>834</v>
+        <v>866</v>
       </c>
       <c r="P54" s="2" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="55" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A55" s="2" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="B55" s="16">
         <v>2020</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>540</v>
+        <v>525</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="E55" s="11" t="s">
-        <v>619</v>
+        <v>603</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>542</v>
+        <v>527</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="J55" s="3"/>
       <c r="K55" s="3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="L55" s="3"/>
       <c r="N55" s="2" t="s">
-        <v>745</v>
+        <v>726</v>
       </c>
       <c r="O55" s="2" t="s">
-        <v>806</v>
+        <v>779</v>
       </c>
       <c r="P55" s="2" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="56" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" s="2" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="B56" s="16">
         <v>2020</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>396</v>
+        <v>386</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="E56" s="11" t="s">
-        <v>620</v>
+        <v>604</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="K56" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="L56" s="3"/>
       <c r="M56" s="3" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>746</v>
+        <v>727</v>
       </c>
       <c r="O56" s="2" t="s">
-        <v>286</v>
+        <v>867</v>
       </c>
       <c r="P56" s="2" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="57" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A57" s="2" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="B57" s="16">
         <v>2020</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="D57" s="7" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E57" s="11" t="s">
-        <v>621</v>
+        <v>605</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>542</v>
+        <v>527</v>
       </c>
       <c r="K57" s="3" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="L57" s="3"/>
       <c r="N57" s="2" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="O57" s="2" t="s">
-        <v>835</v>
+        <v>827</v>
       </c>
       <c r="P57" s="2" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="58" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="2" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="B58" s="16">
         <v>2021</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>401</v>
+        <v>391</v>
       </c>
       <c r="D58" s="7" t="s">
         <v>31</v>
       </c>
       <c r="E58" s="11" t="s">
-        <v>622</v>
+        <v>606</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>542</v>
+        <v>527</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>33</v>
@@ -7033,204 +7027,204 @@
         <v>32</v>
       </c>
       <c r="O58" s="2" t="s">
-        <v>807</v>
+        <v>780</v>
       </c>
       <c r="P58" s="2" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="59" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="59" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="2" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B59" s="16">
         <v>2021</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>402</v>
+        <v>392</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="E59" s="11" t="s">
-        <v>623</v>
+        <v>607</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>541</v>
+        <v>526</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="H59" s="3"/>
       <c r="N59" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="O59" s="2" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="P59" s="2" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="60" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="2" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="B60" s="16">
         <v>2021</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>404</v>
+        <v>394</v>
       </c>
       <c r="D60" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="E60" s="11" t="s">
+        <v>608</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="G60" s="3" t="s">
         <v>106</v>
-      </c>
-      <c r="E60" s="11" t="s">
-        <v>624</v>
-      </c>
-      <c r="F60" s="2" t="s">
-        <v>546</v>
-      </c>
-      <c r="G60" s="3" t="s">
-        <v>107</v>
       </c>
       <c r="H60" s="3"/>
       <c r="K60" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="N60" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O60" s="2" t="s">
-        <v>836</v>
+        <v>868</v>
       </c>
       <c r="P60" s="2" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="61" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="2" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B61" s="16">
         <v>2021</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>406</v>
+        <v>396</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E61" s="11" t="s">
-        <v>625</v>
+        <v>609</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>547</v>
+        <v>532</v>
       </c>
       <c r="K61" s="3" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="L61" s="3"/>
       <c r="N61" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="O61" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="P61" s="2" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="62" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A62" s="2" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="B62" s="16">
         <v>2021</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>403</v>
+        <v>393</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E62" s="11" t="s">
-        <v>626</v>
+        <v>610</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="K62" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="L62" s="3"/>
       <c r="M62" s="3" t="s">
-        <v>437</v>
+        <v>427</v>
       </c>
       <c r="N62" s="2" t="s">
-        <v>747</v>
+        <v>728</v>
       </c>
       <c r="O62" s="2" t="s">
-        <v>808</v>
+        <v>835</v>
       </c>
       <c r="P62" s="2" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="63" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A63" s="2" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="B63" s="16">
         <v>2021</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>405</v>
+        <v>395</v>
       </c>
       <c r="D63" s="7" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E63" s="11" t="s">
-        <v>627</v>
+        <v>611</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>544</v>
+        <v>529</v>
       </c>
       <c r="K63" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="L63" s="3"/>
       <c r="N63" s="2" t="s">
-        <v>748</v>
+        <v>729</v>
       </c>
       <c r="O63" s="2" t="s">
-        <v>837</v>
+        <v>869</v>
       </c>
       <c r="P63" s="2" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="R63" s="2" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="64" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="64" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="2" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B64" s="16">
         <v>2022</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="D64" s="7" t="s">
         <v>38</v>
       </c>
       <c r="E64" s="7" t="s">
-        <v>548</v>
+        <v>533</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="G64" s="3" t="s">
         <v>40</v>
@@ -7241,290 +7235,290 @@
       </c>
       <c r="L64" s="3"/>
       <c r="M64" s="3" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="N64" s="2" t="s">
         <v>39</v>
       </c>
       <c r="O64" s="2" t="s">
-        <v>838</v>
+        <v>793</v>
       </c>
       <c r="P64" s="2" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="65" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="65" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="2" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="B65" s="16">
         <v>2022</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="D65" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="E65" s="11" t="s">
+        <v>612</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="G65" s="3" t="s">
         <v>112</v>
-      </c>
-      <c r="E65" s="11" t="s">
-        <v>628</v>
-      </c>
-      <c r="F65" s="2" t="s">
-        <v>542</v>
-      </c>
-      <c r="G65" s="3" t="s">
-        <v>113</v>
       </c>
       <c r="H65" s="3"/>
       <c r="K65" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="L65" s="3"/>
       <c r="M65" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="N65" s="2" t="s">
-        <v>749</v>
+        <v>730</v>
       </c>
       <c r="O65" s="2" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="P65" s="2" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="66" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="66" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="2" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="B66" s="16">
         <v>2022</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>411</v>
+        <v>401</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E66" s="11" t="s">
-        <v>629</v>
+        <v>613</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>542</v>
+        <v>527</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H66" s="3"/>
       <c r="N66" s="2" t="s">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="O66" s="2" t="s">
-        <v>840</v>
+        <v>870</v>
       </c>
       <c r="P66" s="2" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="67" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="67" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="2" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="B67" s="16">
         <v>2022</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>412</v>
+        <v>402</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E67" s="11" t="s">
-        <v>630</v>
+        <v>614</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="K67" s="3" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="L67" s="3"/>
       <c r="M67" s="3" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="N67" s="2" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="O67" s="2" t="s">
-        <v>841</v>
+        <v>794</v>
       </c>
       <c r="P67" s="2" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="68" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="68" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="2" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="B68" s="16">
         <v>2022</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>409</v>
+        <v>399</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="E68" s="11" t="s">
-        <v>631</v>
+        <v>615</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="K68" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="L68" s="3"/>
       <c r="M68" s="3" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="N68" s="2" t="s">
-        <v>750</v>
+        <v>731</v>
       </c>
       <c r="O68" s="2" t="s">
-        <v>871</v>
+        <v>823</v>
       </c>
       <c r="P68" s="2" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="69" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="69" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="2" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B69" s="16">
         <v>2022</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="D69" s="7" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E69" s="11" t="s">
-        <v>632</v>
+        <v>616</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>542</v>
+        <v>527</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="H69" s="3"/>
       <c r="I69" s="3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="J69" s="3"/>
       <c r="N69" s="2" t="s">
-        <v>751</v>
+        <v>822</v>
       </c>
       <c r="O69" s="2" t="s">
-        <v>842</v>
+        <v>857</v>
       </c>
       <c r="P69" s="2" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="70" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="70" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="2" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="B70" s="16">
         <v>2022</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>408</v>
+        <v>398</v>
       </c>
       <c r="D70" s="7" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E70" s="11" t="s">
-        <v>633</v>
+        <v>617</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="K70" s="3" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="L70" s="3"/>
       <c r="M70" s="2" t="s">
-        <v>438</v>
+        <v>428</v>
       </c>
       <c r="N70" s="2" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="O70" s="2" t="s">
-        <v>809</v>
+        <v>781</v>
       </c>
       <c r="P70" s="2" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="71" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="71" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="2" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="B71" s="16">
         <v>2022</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>413</v>
+        <v>403</v>
       </c>
       <c r="D71" s="7" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E71" s="11" t="s">
-        <v>634</v>
+        <v>618</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="K71" s="3" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="L71" s="3"/>
       <c r="M71" s="3" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="N71" s="2" t="s">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="O71" s="2" t="s">
-        <v>843</v>
+        <v>871</v>
       </c>
       <c r="P71" s="2" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="72" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="72" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="2" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="B72" s="16">
         <v>2023</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>414</v>
+        <v>404</v>
       </c>
       <c r="D72" s="14" t="s">
         <v>20</v>
       </c>
       <c r="E72" s="9" t="s">
-        <v>549</v>
+        <v>534</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>550</v>
+        <v>535</v>
       </c>
       <c r="G72" s="3" t="s">
         <v>21</v>
@@ -7535,236 +7529,236 @@
       </c>
       <c r="L72" s="3"/>
       <c r="N72" s="2" t="s">
-        <v>752</v>
+        <v>732</v>
       </c>
       <c r="O72" s="2" t="s">
-        <v>877</v>
+        <v>809</v>
       </c>
       <c r="P72" s="2" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="R72" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="73" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="2" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="B73" s="16">
         <v>2023</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>415</v>
+        <v>405</v>
       </c>
       <c r="D73" s="9" t="s">
         <v>24</v>
       </c>
       <c r="E73" s="11" t="s">
-        <v>635</v>
+        <v>619</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>542</v>
+        <v>527</v>
       </c>
       <c r="K73" s="3" t="s">
         <v>25</v>
       </c>
       <c r="L73" s="3"/>
       <c r="N73" s="2" t="s">
-        <v>753</v>
+        <v>733</v>
       </c>
       <c r="O73" s="2" t="s">
-        <v>878</v>
+        <v>875</v>
       </c>
       <c r="P73" s="2" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="74" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="74" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="2" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B74" s="16">
         <v>2023</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>417</v>
+        <v>407</v>
       </c>
       <c r="D74" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E74" s="11" t="s">
+        <v>620</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="K74" s="3" t="s">
         <v>55</v>
-      </c>
-      <c r="E74" s="11" t="s">
-        <v>636</v>
-      </c>
-      <c r="F74" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="K74" s="3" t="s">
-        <v>56</v>
       </c>
       <c r="L74" s="3"/>
       <c r="M74" s="3" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="N74" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="O74" s="2" t="s">
-        <v>259</v>
+        <v>843</v>
       </c>
       <c r="P74" s="2" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="75" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="75" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="2" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="B75" s="16">
         <v>2023</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>418</v>
+        <v>408</v>
       </c>
       <c r="D75" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="E75" s="11" t="s">
+        <v>621</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="K75" s="3" t="s">
         <v>58</v>
-      </c>
-      <c r="E75" s="11" t="s">
-        <v>637</v>
-      </c>
-      <c r="F75" s="2" t="s">
-        <v>544</v>
-      </c>
-      <c r="K75" s="3" t="s">
-        <v>59</v>
       </c>
       <c r="L75" s="3"/>
       <c r="N75" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="O75" s="2" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="P75" s="2" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="76" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="76" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="2" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="B76" s="16">
         <v>2024</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="D76" s="7" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="E76" s="7" t="s">
-        <v>551</v>
+        <v>536</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>534</v>
+        <v>519</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H76" s="3"/>
       <c r="K76" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L76" s="3"/>
       <c r="M76" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="N76" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O76" s="2" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="P76" s="2" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="77" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="77" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="2" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B77" s="16">
         <v>2023</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>419</v>
+        <v>409</v>
       </c>
       <c r="D77" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="E77" s="7" t="s">
+        <v>537</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="G77" s="3" t="s">
         <v>74</v>
-      </c>
-      <c r="E77" s="7" t="s">
-        <v>552</v>
-      </c>
-      <c r="F77" s="2" t="s">
-        <v>534</v>
-      </c>
-      <c r="G77" s="3" t="s">
-        <v>75</v>
       </c>
       <c r="H77" s="3"/>
       <c r="K77" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="M77" s="3" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="N77" s="2" t="s">
-        <v>445</v>
+        <v>434</v>
       </c>
       <c r="O77" s="2" t="s">
-        <v>844</v>
+        <v>873</v>
       </c>
       <c r="P77" s="2" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="78" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="78" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="2" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="B78" s="16">
         <v>2023</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>421</v>
+        <v>411</v>
       </c>
       <c r="D78" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="E78" s="11" t="s">
+        <v>622</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="K78" s="3" t="s">
         <v>83</v>
-      </c>
-      <c r="E78" s="11" t="s">
-        <v>638</v>
-      </c>
-      <c r="F78" s="2" t="s">
-        <v>544</v>
-      </c>
-      <c r="K78" s="3" t="s">
-        <v>84</v>
       </c>
       <c r="L78" s="3"/>
       <c r="M78" s="3" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="N78" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="O78" s="2" t="s">
-        <v>845</v>
+        <v>795</v>
       </c>
       <c r="P78" s="2" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="79" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="79" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="2" t="s">
         <v>36</v>
       </c>
@@ -7772,704 +7766,704 @@
         <v>2023</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>422</v>
+        <v>412</v>
       </c>
       <c r="D79" s="7" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="E79" s="11" t="s">
-        <v>639</v>
+        <v>623</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>544</v>
+        <v>529</v>
       </c>
       <c r="K79" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L79" s="3"/>
       <c r="N79" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="O79" s="2" t="s">
-        <v>810</v>
+        <v>850</v>
       </c>
       <c r="P79" s="2" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="80" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="80" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="2" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B80" s="16">
         <v>2023</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>423</v>
+        <v>413</v>
       </c>
       <c r="D80" s="7" t="s">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="E80" s="11" t="s">
-        <v>640</v>
+        <v>624</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>553</v>
+        <v>538</v>
       </c>
       <c r="K80" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L80" s="3"/>
       <c r="N80" s="2" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="O80" s="2" t="s">
-        <v>261</v>
+        <v>856</v>
       </c>
       <c r="P80" s="2" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="R80" s="2" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="81" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="81" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="2" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="B81" s="16">
         <v>2023</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>425</v>
+        <v>415</v>
       </c>
       <c r="D81" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E81" s="7" t="s">
-        <v>554</v>
+        <v>539</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="G81" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H81" s="3"/>
       <c r="K81" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L81" s="3"/>
       <c r="M81" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="N81" s="2" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="O81" s="2" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="P81" s="2" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="82" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="82" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A82" s="2" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="B82" s="16">
         <v>2023</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>408</v>
+        <v>398</v>
       </c>
       <c r="D82" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E82" s="12" t="s">
-        <v>555</v>
+        <v>540</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>534</v>
+        <v>519</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H82" s="3"/>
       <c r="K82" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L82" s="3"/>
       <c r="N82" s="2" t="s">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="O82" s="2" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="P82" s="2" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="83" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="83" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A83" s="2" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B83" s="16">
         <v>2023</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>424</v>
+        <v>414</v>
       </c>
       <c r="D83" s="7" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="E83" s="11" t="s">
-        <v>641</v>
+        <v>625</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="K83" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="L83" s="3"/>
       <c r="N83" s="2" t="s">
-        <v>446</v>
+        <v>435</v>
       </c>
       <c r="O83" s="2" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="P83" s="2" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="84" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="84" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A84" s="2" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="B84" s="16">
         <v>2023</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="D84" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="E84" s="11" t="s">
+        <v>626</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="G84" s="3" t="s">
         <v>210</v>
-      </c>
-      <c r="E84" s="11" t="s">
-        <v>642</v>
-      </c>
-      <c r="F84" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="G84" s="3" t="s">
-        <v>212</v>
       </c>
       <c r="H84" s="3"/>
       <c r="I84" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="J84" s="3"/>
       <c r="N84" s="2" t="s">
-        <v>447</v>
+        <v>436</v>
       </c>
       <c r="O84" s="2" t="s">
-        <v>847</v>
+        <v>874</v>
       </c>
       <c r="P84" s="2" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="R84" s="2" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="85" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="85" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A85" s="2" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="B85" s="16">
         <v>2023</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="D85" s="7" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="E85" s="11" t="s">
-        <v>643</v>
+        <v>627</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="J85" s="3"/>
       <c r="N85" s="2" t="s">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="O85" s="2" t="s">
-        <v>811</v>
+        <v>845</v>
       </c>
       <c r="P85" s="2" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="86" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="86" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A86" s="2" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="B86" s="16">
         <v>2023</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>426</v>
+        <v>416</v>
       </c>
       <c r="D86" s="7" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="E86" s="11" t="s">
-        <v>644</v>
+        <v>628</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>542</v>
+        <v>527</v>
       </c>
       <c r="K86" s="3" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="L86" s="3"/>
       <c r="N86" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="O86" s="2" t="s">
-        <v>848</v>
+        <v>838</v>
       </c>
       <c r="P86" s="2" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="87" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="87" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A87" s="2" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="B87" s="16">
         <v>2024</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="D87" s="7" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E87" s="11" t="s">
-        <v>645</v>
+        <v>629</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="K87" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="L87" s="3"/>
       <c r="M87" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="N87" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="O87" s="2" t="s">
+        <v>854</v>
+      </c>
+      <c r="P87" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="N87" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="O87" s="2" t="s">
-        <v>872</v>
-      </c>
-      <c r="P87" s="2" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="88" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="88" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A88" s="2" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="B88" s="16">
         <v>2024</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>431</v>
+        <v>421</v>
       </c>
       <c r="D88" s="7" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E88" s="11" t="s">
-        <v>646</v>
+        <v>630</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="K88" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="L88" s="3"/>
       <c r="M88" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="N88" s="2" t="s">
+        <v>736</v>
+      </c>
+      <c r="O88" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="P88" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="N88" s="2" t="s">
-        <v>756</v>
-      </c>
-      <c r="O88" s="2" t="s">
-        <v>873</v>
-      </c>
-      <c r="P88" s="2" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="89" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="89" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A89" s="2" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="B89" s="16">
         <v>2024</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>408</v>
+        <v>398</v>
       </c>
       <c r="D89" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="E89" s="11" t="s">
+        <v>631</v>
+      </c>
+      <c r="F89" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="K89" s="3" t="s">
         <v>193</v>
-      </c>
-      <c r="E89" s="11" t="s">
-        <v>647</v>
-      </c>
-      <c r="F89" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="K89" s="3" t="s">
-        <v>195</v>
       </c>
       <c r="L89" s="3"/>
       <c r="M89" s="3" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="N89" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="O89" s="2" t="s">
-        <v>849</v>
+        <v>796</v>
       </c>
       <c r="P89" s="2" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="90" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="90" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A90" s="2" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="B90" s="16">
         <v>2024</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>432</v>
+        <v>422</v>
       </c>
       <c r="D90" s="7" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E90" s="7" t="s">
-        <v>556</v>
+        <v>541</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="G90" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="H90" s="3"/>
       <c r="N90" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="O90" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="P90" s="2" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="91" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="91" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A91" s="2" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B91" s="16">
         <v>2024</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>433</v>
+        <v>423</v>
       </c>
       <c r="D91" s="7" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E91" s="11" t="s">
-        <v>648</v>
+        <v>632</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="G91" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="H91" s="3"/>
       <c r="I91" s="3" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="J91" s="3"/>
       <c r="K91" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="L91" s="3"/>
       <c r="M91" s="3" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="N91" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="O91" s="2" t="s">
-        <v>812</v>
+        <v>846</v>
       </c>
       <c r="P91" s="2" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="92" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="92" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A92" s="2" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="B92" s="16">
         <v>2024</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>427</v>
+        <v>417</v>
       </c>
       <c r="D92" s="7" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E92" s="11" t="s">
-        <v>649</v>
+        <v>633</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="K92" s="3" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="L92" s="3"/>
       <c r="M92" s="3" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="N92" s="2" t="s">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="O92" s="2" t="s">
-        <v>850</v>
+        <v>839</v>
       </c>
       <c r="P92" s="2" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="93" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="93" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A93" s="2" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="B93" s="16">
         <v>2024</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>435</v>
+        <v>425</v>
       </c>
       <c r="D93" s="7" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="E93" s="7" t="s">
-        <v>557</v>
+        <v>542</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="G93" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="H93" s="3"/>
       <c r="K93" s="3" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="L93" s="3"/>
       <c r="N93" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="O93" s="2" t="s">
-        <v>851</v>
+        <v>797</v>
       </c>
       <c r="P93" s="2" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="94" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="94" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A94" s="2" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="B94" s="16">
         <v>2024</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>428</v>
+        <v>418</v>
       </c>
       <c r="D94" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="E94" s="11" t="s">
+        <v>634</v>
+      </c>
+      <c r="F94" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="K94" s="3" t="s">
         <v>234</v>
-      </c>
-      <c r="E94" s="11" t="s">
-        <v>650</v>
-      </c>
-      <c r="F94" s="2" t="s">
-        <v>544</v>
-      </c>
-      <c r="K94" s="3" t="s">
-        <v>236</v>
       </c>
       <c r="L94" s="3"/>
       <c r="N94" s="2" t="s">
-        <v>757</v>
+        <v>737</v>
       </c>
       <c r="O94" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="P94" s="2" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="95" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="95" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A95" s="2" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="B95" s="16">
         <v>2024</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>434</v>
+        <v>424</v>
       </c>
       <c r="D95" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="E95" s="11" t="s">
+        <v>635</v>
+      </c>
+      <c r="F95" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="I95" s="3" t="s">
         <v>248</v>
-      </c>
-      <c r="E95" s="11" t="s">
-        <v>651</v>
-      </c>
-      <c r="F95" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="I95" s="3" t="s">
-        <v>250</v>
       </c>
       <c r="J95" s="3"/>
       <c r="N95" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="O95" s="2" t="s">
-        <v>874</v>
+        <v>825</v>
       </c>
       <c r="P95" s="2" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="96" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="96" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A96" s="2" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="B96" s="16">
         <v>2017</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="D96" s="7" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="E96" s="11" t="s">
-        <v>652</v>
+        <v>636</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>544</v>
+        <v>529</v>
       </c>
       <c r="K96" s="2" t="s">
-        <v>449</v>
+        <v>438</v>
       </c>
       <c r="N96" s="2" t="s">
-        <v>580</v>
+        <v>565</v>
       </c>
       <c r="O96" s="2" t="s">
-        <v>813</v>
+        <v>782</v>
       </c>
       <c r="P96" s="2" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="97" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="97" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A97" s="2" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="B97" s="16">
         <v>2017</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>451</v>
+        <v>440</v>
       </c>
       <c r="D97" s="7" t="s">
-        <v>456</v>
+        <v>445</v>
       </c>
       <c r="E97" s="11" t="s">
-        <v>653</v>
+        <v>637</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>544</v>
+        <v>529</v>
       </c>
       <c r="K97" s="2" t="s">
-        <v>452</v>
+        <v>441</v>
       </c>
       <c r="N97" s="2" t="s">
-        <v>581</v>
+        <v>566</v>
       </c>
       <c r="O97" s="2" t="s">
-        <v>880</v>
+        <v>826</v>
       </c>
       <c r="P97" s="2" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="98" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="98" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A98" s="2" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B98" s="16">
         <v>2011</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="D98" s="7" t="s">
-        <v>457</v>
+        <v>446</v>
       </c>
       <c r="E98" s="11" t="s">
-        <v>654</v>
+        <v>638</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>458</v>
+        <v>447</v>
       </c>
       <c r="K98" s="2" t="s">
-        <v>459</v>
+        <v>448</v>
       </c>
       <c r="N98" s="2" t="s">
-        <v>460</v>
+        <v>449</v>
       </c>
       <c r="O98" s="2" t="s">
-        <v>814</v>
+        <v>853</v>
       </c>
       <c r="P98" s="2" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="99" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="99" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A99" s="2" t="s">
         <v>36</v>
       </c>
@@ -8477,127 +8471,127 @@
         <v>2019</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>461</v>
+        <v>450</v>
       </c>
       <c r="D99" s="7" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="E99" s="11" t="s">
-        <v>655</v>
+        <v>639</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="K99" s="2" t="s">
-        <v>463</v>
+        <v>452</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>582</v>
+        <v>567</v>
       </c>
       <c r="O99" s="2" t="s">
-        <v>464</v>
+        <v>453</v>
       </c>
       <c r="P99" s="2" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="100" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="100" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A100" s="2" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="B100" s="16">
         <v>2018</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>465</v>
+        <v>454</v>
       </c>
       <c r="D100" s="7" t="s">
-        <v>466</v>
+        <v>455</v>
       </c>
       <c r="E100" s="11" t="s">
-        <v>656</v>
+        <v>640</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="I100" s="2" t="s">
-        <v>467</v>
+        <v>456</v>
       </c>
       <c r="N100" s="2" t="s">
-        <v>583</v>
+        <v>568</v>
       </c>
       <c r="O100" s="2" t="s">
-        <v>852</v>
+        <v>829</v>
       </c>
       <c r="P100" s="2" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="101" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="101" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A101" s="2" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="B101" s="16">
         <v>2013</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="E101" s="11" t="s">
-        <v>657</v>
+        <v>641</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>469</v>
+        <v>458</v>
       </c>
       <c r="K101" s="2" t="s">
-        <v>470</v>
+        <v>459</v>
       </c>
       <c r="N101" s="2" t="s">
-        <v>471</v>
+        <v>460</v>
       </c>
       <c r="O101" s="2" t="s">
-        <v>870</v>
+        <v>877</v>
       </c>
       <c r="P101" s="2" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="102" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="102" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A102" s="2" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B102" s="16">
         <v>2017</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="D102" s="7" t="s">
-        <v>472</v>
+        <v>461</v>
       </c>
       <c r="E102" s="11" t="s">
-        <v>658</v>
+        <v>642</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>573</v>
+        <v>558</v>
       </c>
       <c r="K102" s="2" t="s">
-        <v>473</v>
+        <v>462</v>
       </c>
       <c r="N102" s="2" t="s">
-        <v>584</v>
+        <v>569</v>
       </c>
       <c r="O102" s="2" t="s">
-        <v>853</v>
+        <v>847</v>
       </c>
       <c r="P102" s="2" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="103" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="103" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A103" s="2" t="s">
         <v>36</v>
       </c>
@@ -8605,255 +8599,255 @@
         <v>2011</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="D103" s="7" t="s">
-        <v>474</v>
+        <v>463</v>
       </c>
       <c r="E103" s="11" t="s">
-        <v>659</v>
+        <v>643</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>544</v>
+        <v>529</v>
       </c>
       <c r="K103" s="2" t="s">
-        <v>475</v>
+        <v>464</v>
       </c>
       <c r="N103" s="2" t="s">
-        <v>585</v>
+        <v>570</v>
       </c>
       <c r="O103" s="2" t="s">
-        <v>476</v>
+        <v>465</v>
       </c>
       <c r="P103" s="2" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="104" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="104" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A104" s="2" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B104" s="16">
         <v>2011</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>478</v>
+        <v>467</v>
       </c>
       <c r="D104" s="7" t="s">
-        <v>479</v>
+        <v>468</v>
       </c>
       <c r="E104" s="7" t="s">
-        <v>574</v>
+        <v>559</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>477</v>
+        <v>466</v>
       </c>
       <c r="N104" s="2" t="s">
-        <v>480</v>
+        <v>469</v>
       </c>
       <c r="O104" s="2" t="s">
-        <v>476</v>
+        <v>465</v>
       </c>
       <c r="P104" s="2" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="105" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="105" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A105" s="2" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B105" s="16">
         <v>2012</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>481</v>
+        <v>470</v>
       </c>
       <c r="E105" s="11" t="s">
-        <v>660</v>
+        <v>644</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="K105" s="2" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="N105" s="2" t="s">
-        <v>592</v>
+        <v>577</v>
       </c>
       <c r="O105" s="2" t="s">
-        <v>476</v>
+        <v>465</v>
       </c>
       <c r="P105" s="2" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="106" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="106" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A106" s="2" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B106" s="16">
         <v>2014</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="D106" s="7" t="s">
-        <v>485</v>
+        <v>474</v>
       </c>
       <c r="E106" s="7" t="s">
-        <v>575</v>
+        <v>560</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>487</v>
+        <v>476</v>
       </c>
       <c r="N106" s="2" t="s">
-        <v>586</v>
+        <v>571</v>
       </c>
       <c r="O106" s="2" t="s">
-        <v>486</v>
+        <v>475</v>
       </c>
       <c r="P106" s="2" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="107" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="107" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A107" s="2" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="B107" s="16">
         <v>2017</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>488</v>
+        <v>477</v>
       </c>
       <c r="D107" s="7" t="s">
-        <v>489</v>
+        <v>478</v>
       </c>
       <c r="E107" s="11" t="s">
-        <v>661</v>
+        <v>645</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>542</v>
+        <v>527</v>
       </c>
       <c r="K107" s="2" t="s">
-        <v>490</v>
+        <v>479</v>
       </c>
       <c r="N107" s="2" t="s">
-        <v>587</v>
+        <v>572</v>
       </c>
       <c r="O107" s="2" t="s">
-        <v>491</v>
+        <v>480</v>
       </c>
       <c r="P107" s="2" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="108" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="108" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A108" s="2" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B108" s="16">
         <v>2017</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>492</v>
+        <v>481</v>
       </c>
       <c r="D108" s="7" t="s">
+        <v>561</v>
+      </c>
+      <c r="E108" s="12" t="s">
+        <v>562</v>
+      </c>
+      <c r="F108" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="G108" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="N108" s="10" t="s">
         <v>576</v>
       </c>
-      <c r="E108" s="12" t="s">
-        <v>577</v>
-      </c>
-      <c r="F108" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="G108" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="N108" s="10" t="s">
-        <v>591</v>
-      </c>
       <c r="O108" s="2" t="s">
-        <v>854</v>
+        <v>798</v>
       </c>
       <c r="P108" s="2" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="109" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="109" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A109" s="2" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="B109" s="16">
         <v>2017</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>494</v>
+        <v>483</v>
       </c>
       <c r="D109" s="7" t="s">
-        <v>495</v>
+        <v>484</v>
       </c>
       <c r="E109" s="11" t="s">
-        <v>662</v>
+        <v>646</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="K109" s="2" t="s">
-        <v>496</v>
+        <v>485</v>
       </c>
       <c r="N109" s="2" t="s">
-        <v>588</v>
+        <v>573</v>
       </c>
       <c r="O109" s="2" t="s">
-        <v>855</v>
+        <v>799</v>
       </c>
       <c r="P109" s="2" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="110" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="110" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A110" s="2" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B110" s="16">
         <v>2016</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="D110" s="7" t="s">
-        <v>497</v>
+        <v>486</v>
       </c>
       <c r="E110" s="11" t="s">
-        <v>578</v>
+        <v>563</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>498</v>
+        <v>487</v>
       </c>
       <c r="N110" s="2" t="s">
-        <v>589</v>
+        <v>574</v>
       </c>
       <c r="O110" s="2" t="s">
-        <v>499</v>
+        <v>488</v>
       </c>
       <c r="P110" s="2" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="111" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="111" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A111" s="2" t="s">
         <v>36</v>
       </c>
@@ -8861,96 +8855,96 @@
         <v>2018</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>500</v>
+        <v>489</v>
       </c>
       <c r="D111" s="7" t="s">
-        <v>501</v>
+        <v>490</v>
       </c>
       <c r="E111" s="11" t="s">
-        <v>663</v>
+        <v>647</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>572</v>
+        <v>557</v>
       </c>
       <c r="K111" s="2" t="s">
-        <v>502</v>
+        <v>491</v>
       </c>
       <c r="N111" s="2" t="s">
-        <v>590</v>
+        <v>575</v>
       </c>
       <c r="O111" s="2" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="P111" s="2" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="112" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="112" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A112" s="2" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="B112" s="16">
         <v>2024</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>434</v>
+        <v>424</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>503</v>
+        <v>492</v>
       </c>
       <c r="E112" s="11" t="s">
-        <v>664</v>
+        <v>648</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>542</v>
+        <v>527</v>
       </c>
       <c r="K112" s="2" t="s">
-        <v>504</v>
+        <v>493</v>
       </c>
       <c r="N112" s="2" t="s">
-        <v>505</v>
+        <v>494</v>
       </c>
       <c r="O112" s="2" t="s">
-        <v>875</v>
+        <v>833</v>
       </c>
       <c r="P112" s="2" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="113" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="113" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A113" s="2" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B113" s="16">
         <v>2018</v>
       </c>
       <c r="C113" s="18" t="s">
-        <v>768</v>
+        <v>747</v>
       </c>
       <c r="D113" s="7" t="s">
-        <v>558</v>
+        <v>543</v>
       </c>
       <c r="E113" s="12" t="s">
-        <v>559</v>
+        <v>544</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>560</v>
+        <v>545</v>
       </c>
       <c r="G113" s="3" t="s">
-        <v>561</v>
+        <v>546</v>
       </c>
       <c r="H113" s="3"/>
       <c r="N113" s="2" t="s">
-        <v>562</v>
+        <v>547</v>
       </c>
       <c r="O113" s="2" t="s">
-        <v>259</v>
+        <v>843</v>
       </c>
       <c r="P113" s="2" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="114" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="114" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A114" s="2" t="s">
         <v>36</v>
       </c>
@@ -8958,300 +8952,300 @@
         <v>2018</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>567</v>
+        <v>552</v>
       </c>
       <c r="D114" s="7" t="s">
-        <v>566</v>
+        <v>551</v>
       </c>
       <c r="E114" s="7" t="s">
-        <v>568</v>
+        <v>553</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>539</v>
+        <v>524</v>
       </c>
       <c r="G114" s="3" t="s">
-        <v>569</v>
+        <v>554</v>
       </c>
       <c r="H114" s="3"/>
       <c r="N114" s="2" t="s">
-        <v>570</v>
+        <v>555</v>
       </c>
       <c r="O114" s="2" t="s">
-        <v>857</v>
+        <v>800</v>
       </c>
       <c r="P114" s="2" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="115" spans="1:16" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="115" spans="1:16" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A115" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B115">
         <v>2012</v>
       </c>
       <c r="C115" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="D115" t="s">
-        <v>665</v>
+        <v>649</v>
       </c>
       <c r="E115" t="s">
-        <v>709</v>
+        <v>693</v>
       </c>
       <c r="F115" t="s">
-        <v>469</v>
+        <v>458</v>
       </c>
       <c r="I115" s="2"/>
       <c r="J115" s="2"/>
       <c r="K115" t="s">
-        <v>666</v>
+        <v>650</v>
       </c>
       <c r="N115" t="s">
-        <v>766</v>
+        <v>745</v>
       </c>
       <c r="O115" s="2" t="s">
-        <v>858</v>
+        <v>801</v>
       </c>
       <c r="P115" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="116" spans="1:16" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="116" spans="1:16" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A116" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B116">
         <v>2012</v>
       </c>
       <c r="C116" t="s">
-        <v>667</v>
+        <v>651</v>
       </c>
       <c r="D116" t="s">
-        <v>668</v>
+        <v>652</v>
       </c>
       <c r="E116" s="11" t="s">
-        <v>710</v>
+        <v>694</v>
       </c>
       <c r="F116" t="s">
-        <v>458</v>
+        <v>447</v>
       </c>
       <c r="I116" s="2"/>
       <c r="J116" s="2"/>
       <c r="K116" s="2" t="s">
-        <v>669</v>
+        <v>653</v>
       </c>
       <c r="L116" s="2"/>
       <c r="M116" s="2"/>
       <c r="N116" t="s">
-        <v>670</v>
+        <v>654</v>
       </c>
       <c r="O116" s="2" t="s">
-        <v>859</v>
+        <v>828</v>
       </c>
       <c r="P116" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="117" spans="1:16" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="117" spans="1:16" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A117" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B117">
         <v>2013</v>
       </c>
       <c r="C117" t="s">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>724</v>
+        <v>708</v>
       </c>
       <c r="E117" t="s">
-        <v>711</v>
+        <v>695</v>
       </c>
       <c r="F117" t="s">
-        <v>542</v>
+        <v>527</v>
       </c>
       <c r="I117" s="2"/>
       <c r="J117" s="2"/>
       <c r="K117" s="2" t="s">
-        <v>672</v>
+        <v>656</v>
       </c>
       <c r="L117" s="2"/>
       <c r="M117" s="2"/>
       <c r="N117" t="s">
-        <v>671</v>
+        <v>655</v>
       </c>
       <c r="O117" s="2" t="s">
-        <v>860</v>
+        <v>802</v>
       </c>
       <c r="P117" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="118" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="118" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A118" s="2" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B118" s="16">
         <v>2014</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>674</v>
+        <v>658</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>673</v>
+        <v>657</v>
       </c>
       <c r="E118" s="11" t="s">
-        <v>712</v>
+        <v>696</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>542</v>
+        <v>527</v>
       </c>
       <c r="K118" s="2" t="s">
-        <v>675</v>
+        <v>659</v>
       </c>
       <c r="N118" s="2" t="s">
-        <v>676</v>
+        <v>660</v>
       </c>
       <c r="O118" s="2" t="s">
-        <v>861</v>
+        <v>803</v>
       </c>
       <c r="P118" s="2" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="119" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="119" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A119" s="2" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B119" s="16">
         <v>2014</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>678</v>
+        <v>662</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>677</v>
+        <v>661</v>
       </c>
       <c r="E119" s="7" t="s">
-        <v>713</v>
+        <v>697</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>542</v>
+        <v>527</v>
       </c>
       <c r="K119" s="2" t="s">
-        <v>679</v>
+        <v>663</v>
       </c>
       <c r="N119" s="2" t="s">
-        <v>765</v>
+        <v>744</v>
       </c>
       <c r="O119" s="2" t="s">
-        <v>815</v>
+        <v>783</v>
       </c>
       <c r="P119" s="2" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="120" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="120" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A120" s="2" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="B120" s="16">
         <v>2015</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>714</v>
+        <v>698</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>680</v>
+        <v>664</v>
       </c>
       <c r="E120" s="11" t="s">
-        <v>715</v>
+        <v>699</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>542</v>
+        <v>527</v>
       </c>
       <c r="K120" s="2" t="s">
-        <v>681</v>
+        <v>665</v>
       </c>
       <c r="N120" s="2" t="s">
-        <v>764</v>
+        <v>743</v>
       </c>
       <c r="O120" s="2" t="s">
-        <v>876</v>
+        <v>808</v>
       </c>
       <c r="P120" s="2" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="121" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="121" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A121" s="2" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="B121" s="16">
         <v>2016</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>683</v>
+        <v>667</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>682</v>
+        <v>666</v>
       </c>
       <c r="E121" s="11" t="s">
-        <v>716</v>
+        <v>700</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>542</v>
+        <v>527</v>
       </c>
       <c r="K121" s="3" t="s">
-        <v>684</v>
+        <v>668</v>
       </c>
       <c r="L121" s="3"/>
       <c r="N121" s="2" t="s">
-        <v>763</v>
+        <v>742</v>
       </c>
       <c r="O121" s="2" t="s">
-        <v>816</v>
+        <v>784</v>
       </c>
       <c r="P121" s="2" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="122" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="122" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A122" s="2" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B122" s="16">
         <v>2016</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>686</v>
+        <v>670</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>685</v>
+        <v>669</v>
       </c>
       <c r="E122" s="11" t="s">
-        <v>717</v>
+        <v>701</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>542</v>
+        <v>527</v>
       </c>
       <c r="K122" s="3" t="s">
-        <v>687</v>
+        <v>671</v>
       </c>
       <c r="L122" s="3"/>
       <c r="N122" s="2" t="s">
-        <v>762</v>
+        <v>741</v>
       </c>
       <c r="O122" s="2" t="s">
-        <v>726</v>
+        <v>848</v>
       </c>
       <c r="P122" s="2" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="123" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="123" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A123" s="2" t="s">
         <v>36</v>
       </c>
@@ -9259,258 +9253,258 @@
         <v>2016</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>688</v>
+        <v>672</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>691</v>
+        <v>675</v>
       </c>
       <c r="E123" s="11" t="s">
-        <v>718</v>
+        <v>702</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>542</v>
+        <v>527</v>
       </c>
       <c r="K123" s="3" t="s">
-        <v>689</v>
+        <v>673</v>
       </c>
       <c r="L123" s="3"/>
       <c r="N123" s="2" t="s">
-        <v>690</v>
+        <v>674</v>
       </c>
       <c r="O123" s="2" t="s">
-        <v>727</v>
+        <v>851</v>
       </c>
       <c r="P123" s="2" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="124" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="124" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A124" s="2" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="B124" s="16">
         <v>2016</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>692</v>
+        <v>676</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>693</v>
+        <v>677</v>
       </c>
       <c r="E124" s="11" t="s">
-        <v>719</v>
+        <v>703</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="K124" s="3" t="s">
-        <v>695</v>
+        <v>679</v>
       </c>
       <c r="L124" s="3"/>
       <c r="N124" s="2" t="s">
-        <v>694</v>
+        <v>678</v>
       </c>
       <c r="O124" s="2" t="s">
-        <v>817</v>
+        <v>785</v>
       </c>
       <c r="P124" s="2" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="125" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="125" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A125" s="2" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B125" s="16">
         <v>2016</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>697</v>
+        <v>681</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>696</v>
+        <v>680</v>
       </c>
       <c r="E125" s="7" t="s">
-        <v>720</v>
+        <v>704</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="G125" s="3" t="s">
-        <v>698</v>
+        <v>682</v>
       </c>
       <c r="H125" s="3"/>
       <c r="N125" s="2" t="s">
-        <v>761</v>
+        <v>740</v>
       </c>
       <c r="O125" s="2" t="s">
-        <v>863</v>
+        <v>804</v>
       </c>
       <c r="P125" s="2" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="126" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="126" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A126" s="2" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="B126" s="16">
         <v>2019</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>699</v>
+        <v>683</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>725</v>
+        <v>709</v>
       </c>
       <c r="E126" s="11" t="s">
-        <v>721</v>
+        <v>705</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>542</v>
+        <v>527</v>
       </c>
       <c r="K126" s="3" t="s">
-        <v>700</v>
+        <v>684</v>
       </c>
       <c r="L126" s="3"/>
       <c r="N126" s="2" t="s">
-        <v>760</v>
+        <v>739</v>
       </c>
       <c r="O126" s="2" t="s">
-        <v>862</v>
+        <v>849</v>
       </c>
       <c r="P126" s="2" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="127" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="127" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A127" s="2" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="B127" s="16">
         <v>2021</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>702</v>
+        <v>686</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>701</v>
+        <v>685</v>
       </c>
       <c r="E127" s="11" t="s">
-        <v>722</v>
+        <v>706</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>542</v>
+        <v>527</v>
       </c>
       <c r="K127" s="3" t="s">
-        <v>704</v>
+        <v>688</v>
       </c>
       <c r="L127" s="3"/>
       <c r="N127" s="2" t="s">
-        <v>759</v>
+        <v>738</v>
       </c>
       <c r="O127" s="2" t="s">
-        <v>703</v>
+        <v>687</v>
       </c>
       <c r="P127" s="2" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="128" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="128" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A128" s="2" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B128" s="16">
         <v>2022</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>706</v>
+        <v>690</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>705</v>
+        <v>689</v>
       </c>
       <c r="E128" s="11" t="s">
-        <v>723</v>
+        <v>707</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="K128" s="3" t="s">
-        <v>708</v>
+        <v>692</v>
       </c>
       <c r="L128" s="3"/>
       <c r="N128" s="2" t="s">
-        <v>707</v>
+        <v>691</v>
       </c>
       <c r="O128" s="2" t="s">
-        <v>728</v>
+        <v>710</v>
       </c>
       <c r="P128" s="2" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="129" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="129" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A129" s="2" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="B129" s="16">
         <v>2024</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>772</v>
+        <v>751</v>
       </c>
       <c r="D129" s="7" t="s">
-        <v>773</v>
+        <v>752</v>
       </c>
       <c r="E129" s="7" t="s">
-        <v>785</v>
+        <v>764</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>542</v>
+        <v>527</v>
       </c>
       <c r="N129" s="2" t="s">
-        <v>782</v>
+        <v>761</v>
       </c>
       <c r="O129" s="2" t="s">
-        <v>864</v>
+        <v>834</v>
       </c>
       <c r="P129" s="2" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="130" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="130" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A130" s="2" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B130" s="16">
         <v>2024</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>774</v>
+        <v>753</v>
       </c>
       <c r="D130" s="7" t="s">
-        <v>775</v>
+        <v>754</v>
       </c>
       <c r="E130" s="7" t="s">
-        <v>776</v>
+        <v>755</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>542</v>
+        <v>527</v>
       </c>
       <c r="K130" s="3" t="s">
-        <v>783</v>
+        <v>762</v>
       </c>
       <c r="N130" s="2" t="s">
-        <v>786</v>
+        <v>765</v>
       </c>
       <c r="O130" s="2" t="s">
-        <v>777</v>
+        <v>756</v>
       </c>
       <c r="P130" s="2" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="131" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="131" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A131" s="2" t="s">
         <v>36</v>
       </c>
@@ -9518,28 +9512,28 @@
         <v>2024</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>778</v>
+        <v>757</v>
       </c>
       <c r="D131" s="7" t="s">
-        <v>779</v>
+        <v>758</v>
       </c>
       <c r="E131" s="7" t="s">
-        <v>780</v>
+        <v>759</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>542</v>
+        <v>527</v>
       </c>
       <c r="K131" s="3" t="s">
-        <v>784</v>
+        <v>763</v>
       </c>
       <c r="N131" s="2" t="s">
-        <v>787</v>
+        <v>766</v>
       </c>
       <c r="O131" s="2" t="s">
-        <v>781</v>
+        <v>760</v>
       </c>
       <c r="P131" s="2" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
     </row>
   </sheetData>
@@ -9724,7 +9718,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C30D7E91-F216-4F5D-A39B-8B15371B8306}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
